--- a/AAII_Financials/Quarterly/GANX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GANX_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="92">
   <si>
     <t>GANX</t>
   </si>
@@ -656,79 +656,80 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44012</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>43921</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
@@ -741,8 +742,11 @@
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -750,20 +754,20 @@
         <v>3</v>
       </c>
       <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
         <v>100</v>
       </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
       <c r="G8" s="3">
         <v>0</v>
       </c>
       <c r="H8" s="3">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3">
         <v>100</v>
       </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
       <c r="J8" s="3">
         <v>0</v>
       </c>
@@ -771,19 +775,19 @@
         <v>0</v>
       </c>
       <c r="L8" s="3">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3">
         <v>100</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
-      </c>
       <c r="N8" s="3">
         <v>0</v>
       </c>
       <c r="O8" s="3">
         <v>0</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
+      <c r="P8" s="3">
+        <v>0</v>
       </c>
       <c r="Q8" s="3" t="s">
         <v>3</v>
@@ -791,14 +795,17 @@
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S8" s="3">
-        <v>0</v>
+      <c r="S8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -853,8 +860,11 @@
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -909,8 +919,11 @@
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -931,49 +944,50 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E12" s="3">
         <v>4000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>2800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>2300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>2000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>2600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>2500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1400</v>
-      </c>
-      <c r="N12" s="3">
-        <v>400</v>
       </c>
       <c r="O12" s="3">
         <v>400</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>3</v>
+      <c r="P12" s="3">
+        <v>400</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>3</v>
@@ -987,8 +1001,11 @@
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1043,8 +1060,11 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1099,31 +1119,34 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
         <v>0</v>
       </c>
-      <c r="E15" s="3">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3">
-        <v>0</v>
-      </c>
-      <c r="H15" s="3">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3">
-        <v>0</v>
+      <c r="E15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1155,8 +1178,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1174,49 +1200,50 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E17" s="3">
         <v>7700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>5300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5300</v>
-      </c>
-      <c r="I17" s="3">
-        <v>3300</v>
       </c>
       <c r="J17" s="3">
         <v>3300</v>
       </c>
       <c r="K17" s="3">
+        <v>3300</v>
+      </c>
+      <c r="L17" s="3">
         <v>4700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2500</v>
-      </c>
-      <c r="N17" s="3">
-        <v>500</v>
       </c>
       <c r="O17" s="3">
         <v>500</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
+      <c r="P17" s="3">
+        <v>500</v>
       </c>
       <c r="Q17" s="3" t="s">
         <v>3</v>
@@ -1230,8 +1257,11 @@
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1239,40 +1269,40 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="F18" s="3">
         <v>-5200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-4600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-4800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-5200</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-3300</v>
       </c>
       <c r="J18" s="3">
         <v>-3300</v>
       </c>
       <c r="K18" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="L18" s="3">
         <v>-4700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-3500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2500</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-500</v>
       </c>
       <c r="O18" s="3">
         <v>-500</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
+      <c r="P18" s="3">
+        <v>-500</v>
       </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
@@ -1286,8 +1316,11 @@
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1308,8 +1341,9 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1320,19 +1354,19 @@
         <v>100</v>
       </c>
       <c r="F20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>200</v>
-      </c>
-      <c r="H20" s="3">
-        <v>100</v>
       </c>
       <c r="I20" s="3">
         <v>100</v>
       </c>
       <c r="J20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1347,11 +1381,11 @@
         <v>0</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-100</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1364,8 +1398,11 @@
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1373,41 +1410,41 @@
         <v>3</v>
       </c>
       <c r="E21" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="F21" s="3">
         <v>-5100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-4600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-4500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-5100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-3300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-3200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-4700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-3600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-2400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-600</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1420,8 +1457,11 @@
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1476,50 +1516,53 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-7700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-5100</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-4600</v>
       </c>
       <c r="G23" s="3">
         <v>-4600</v>
       </c>
       <c r="H23" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="I23" s="3">
         <v>-5100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-3300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-3200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-4700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-3600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-600</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1532,8 +1575,11 @@
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1544,11 +1590,11 @@
         <v>0</v>
       </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
         <v>0</v>
       </c>
@@ -1573,8 +1619,8 @@
       <c r="O24" s="3">
         <v>0</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
+      <c r="P24" s="3">
+        <v>0</v>
       </c>
       <c r="Q24" s="3" t="s">
         <v>3</v>
@@ -1588,8 +1634,11 @@
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1644,50 +1693,53 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-7700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-5100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-4700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-4600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-5100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-3300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-3200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-4700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-3600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-600</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1700,50 +1752,53 @@
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-7700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-5100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-4700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-4600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-5100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-3300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-3200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-4700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-3600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-600</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1756,8 +1811,11 @@
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1812,8 +1870,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1868,8 +1929,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1924,8 +1988,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1980,8 +2047,11 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1992,19 +2062,19 @@
         <v>-100</v>
       </c>
       <c r="F32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>-200</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-100</v>
       </c>
       <c r="I32" s="3">
         <v>-100</v>
       </c>
       <c r="J32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -2019,11 +2089,11 @@
         <v>0</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>100</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2036,50 +2106,53 @@
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-7700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-5100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-4700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-4600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-5100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-3300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-3200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-4700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-3600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-600</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2092,8 +2165,11 @@
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2148,50 +2224,53 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-7700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-5100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-4700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-4600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-5100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-3300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-3200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-4700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-3600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-600</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2204,55 +2283,58 @@
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44012</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>43921</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2265,8 +2347,11 @@
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2287,8 +2372,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2309,44 +2395,45 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E41" s="3">
         <v>6300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>7300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>10900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>14300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>34300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>36900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>43200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>46600</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2365,38 +2452,41 @@
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E42" s="3">
         <v>9900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>11800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>12800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>11900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>9900</v>
       </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K42" s="3">
+      <c r="K42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L42" s="3">
         <v>40100</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2412,8 +2502,8 @@
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R42" s="3">
-        <v>0</v>
+      <c r="R42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S42" s="3">
         <v>0</v>
@@ -2421,13 +2511,16 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E43" s="3">
         <v>200</v>
@@ -2448,17 +2541,17 @@
         <v>200</v>
       </c>
       <c r="K43" s="3">
+        <v>200</v>
+      </c>
+      <c r="L43" s="3">
         <v>100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>100</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2477,8 +2570,11 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2533,43 +2629,46 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>900</v>
+      </c>
+      <c r="E45" s="3">
         <v>1000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>500</v>
-      </c>
-      <c r="L45" s="3">
-        <v>700</v>
       </c>
       <c r="M45" s="3">
         <v>700</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
+      <c r="N45" s="3">
+        <v>700</v>
       </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
@@ -2589,44 +2688,47 @@
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E46" s="3">
         <v>17300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>19300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>21100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>24300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>25800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>36400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>37700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>41600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>44300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>47400</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2645,29 +2747,32 @@
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E47" s="3">
+      <c r="D47" s="3">
+        <v>0</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3">
         <v>1000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>4900</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2683,8 +2788,8 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -2701,16 +2806,19 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>800</v>
+      </c>
+      <c r="E48" s="3">
         <v>900</v>
-      </c>
-      <c r="E48" s="3">
-        <v>1000</v>
       </c>
       <c r="F48" s="3">
         <v>1000</v>
@@ -2719,26 +2827,26 @@
         <v>1000</v>
       </c>
       <c r="H48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I48" s="3">
         <v>1100</v>
-      </c>
-      <c r="I48" s="3">
-        <v>1200</v>
       </c>
       <c r="J48" s="3">
         <v>1200</v>
       </c>
       <c r="K48" s="3">
-        <v>900</v>
+        <v>1200</v>
       </c>
       <c r="L48" s="3">
         <v>900</v>
       </c>
       <c r="M48" s="3">
+        <v>900</v>
+      </c>
+      <c r="N48" s="3">
         <v>600</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2757,8 +2865,11 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2813,8 +2924,11 @@
       <c r="T49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2869,8 +2983,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2925,8 +3042,11 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2949,7 +3069,7 @@
         <v>0</v>
       </c>
       <c r="J52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K52" s="3">
         <v>100</v>
@@ -2960,8 +3080,8 @@
       <c r="M52" s="3">
         <v>100</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
+      <c r="N52" s="3">
+        <v>100</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
@@ -2981,8 +3101,11 @@
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3037,44 +3160,47 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E54" s="3">
         <v>18300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>21300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>24100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>28300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>31900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>37600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>39000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>42600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>45400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>48000</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3093,8 +3219,11 @@
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3115,8 +3244,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3137,44 +3267,45 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E57" s="3">
         <v>900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>900</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3193,8 +3324,11 @@
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3226,10 +3360,10 @@
         <v>100</v>
       </c>
       <c r="M58" s="3">
-        <v>0</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="N58" s="3">
+        <v>0</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
@@ -3249,43 +3383,46 @@
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E59" s="3">
         <v>4600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2700</v>
-      </c>
-      <c r="L59" s="3">
-        <v>1400</v>
       </c>
       <c r="M59" s="3">
         <v>1400</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
+      <c r="N59" s="3">
+        <v>1400</v>
       </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
@@ -3305,44 +3442,47 @@
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E60" s="3">
         <v>5600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2300</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3361,13 +3501,16 @@
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E61" s="3">
         <v>500</v>
@@ -3382,7 +3525,7 @@
         <v>500</v>
       </c>
       <c r="I61" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="J61" s="3">
         <v>600</v>
@@ -3394,11 +3537,11 @@
         <v>600</v>
       </c>
       <c r="M61" s="3">
+        <v>600</v>
+      </c>
+      <c r="N61" s="3">
         <v>700</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -3417,44 +3560,47 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>600</v>
+      </c>
+      <c r="E62" s="3">
         <v>1100</v>
-      </c>
-      <c r="E62" s="3">
-        <v>600</v>
       </c>
       <c r="F62" s="3">
         <v>600</v>
       </c>
       <c r="G62" s="3">
+        <v>600</v>
+      </c>
+      <c r="H62" s="3">
         <v>800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>900</v>
-      </c>
-      <c r="I62" s="3">
-        <v>1000</v>
       </c>
       <c r="J62" s="3">
         <v>1000</v>
       </c>
       <c r="K62" s="3">
+        <v>1000</v>
+      </c>
+      <c r="L62" s="3">
         <v>800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>600</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3473,8 +3619,11 @@
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3529,8 +3678,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3585,8 +3737,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3641,44 +3796,47 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E66" s="3">
         <v>7200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3600</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3697,8 +3855,11 @@
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3719,8 +3880,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3775,8 +3937,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3831,8 +3996,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3887,8 +4055,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3943,44 +4114,47 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-56100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-51300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-43700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-38500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-33800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-29300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-24200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-20900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-17700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-13000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-9500</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3999,8 +4173,11 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4055,8 +4232,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4111,8 +4291,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4167,44 +4350,47 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E76" s="3">
         <v>11100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>15100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>18900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>22700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>27000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>31800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>34800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>37500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>41400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>44500</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4223,8 +4409,11 @@
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4279,55 +4468,58 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44012</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>43921</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4340,50 +4532,53 @@
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-7700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-5100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-4700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-4600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-5100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-3300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-3200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-4700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-3600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-600</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4396,8 +4591,11 @@
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4418,8 +4616,9 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4459,8 +4658,8 @@
       <c r="O83" s="3">
         <v>0</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
+      <c r="P83" s="3">
+        <v>0</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
@@ -4474,8 +4673,11 @@
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4530,8 +4732,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4586,8 +4791,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4642,8 +4850,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4698,8 +4909,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4754,50 +4968,53 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-5000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-4200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-3900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-3300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-5100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-4100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-3200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-800</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4810,8 +5027,11 @@
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4832,8 +5052,9 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4847,11 +5068,11 @@
         <v>0</v>
       </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
       <c r="I91" s="3">
         <v>0</v>
       </c>
@@ -4873,8 +5094,8 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
+      <c r="P91" s="3">
+        <v>0</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
@@ -4888,8 +5109,11 @@
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4944,8 +5168,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5000,29 +5227,32 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E94" s="3">
         <v>3000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>2100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>100</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
       <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
         <v>-14900</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
       <c r="J94" s="3">
         <v>0</v>
       </c>
@@ -5041,8 +5271,8 @@
       <c r="O94" s="3">
         <v>0</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
+      <c r="P94" s="3">
+        <v>0</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
@@ -5056,8 +5286,11 @@
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5078,8 +5311,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5134,8 +5368,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5190,8 +5427,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5246,8 +5486,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5302,20 +5545,23 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>100</v>
+      </c>
+      <c r="E100" s="3">
         <v>2200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>700</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
         <v>0</v>
       </c>
@@ -5332,20 +5578,20 @@
         <v>0</v>
       </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>-200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>42000</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>1400</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5358,35 +5604,38 @@
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E101" s="3">
         <v>100</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
         <v>200</v>
-      </c>
-      <c r="G101" s="3">
-        <v>-100</v>
       </c>
       <c r="H101" s="3">
         <v>-100</v>
       </c>
       <c r="I101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
         <v>100</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
       <c r="L101" s="3">
         <v>0</v>
       </c>
@@ -5399,8 +5648,8 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>3</v>
+      <c r="P101" s="3">
+        <v>0</v>
       </c>
       <c r="Q101" s="3" t="s">
         <v>3</v>
@@ -5414,50 +5663,53 @@
       <c r="T101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E102" s="3">
         <v>300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-3600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-3400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-20000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-4100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-3400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>39100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>600</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5468,6 +5720,9 @@
         <v>3</v>
       </c>
       <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GANX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GANX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="92">
   <si>
     <t>GANX</t>
   </si>
@@ -656,86 +656,87 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43921</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
@@ -745,8 +746,14 @@
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -757,55 +764,61 @@
         <v>0</v>
       </c>
       <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3">
         <v>100</v>
       </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
       <c r="I8" s="3">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3">
         <v>100</v>
       </c>
-      <c r="J8" s="3">
-        <v>0</v>
-      </c>
-      <c r="K8" s="3">
-        <v>0</v>
-      </c>
       <c r="L8" s="3">
         <v>0</v>
       </c>
       <c r="M8" s="3">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3">
+        <v>0</v>
+      </c>
+      <c r="O8" s="3">
         <v>100</v>
       </c>
-      <c r="N8" s="3">
-        <v>0</v>
-      </c>
-      <c r="O8" s="3">
-        <v>0</v>
-      </c>
       <c r="P8" s="3">
         <v>0</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R8" s="3" t="s">
-        <v>3</v>
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3">
+        <v>0</v>
       </c>
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T8" s="3">
-        <v>0</v>
-      </c>
-      <c r="U8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="T8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V8" s="3">
+        <v>0</v>
+      </c>
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -863,8 +876,14 @@
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -922,8 +941,14 @@
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -945,56 +970,58 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E12" s="3">
         <v>2400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
+        <v>2400</v>
+      </c>
+      <c r="G12" s="3">
         <v>4000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>2800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>2300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>2000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>2600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>1600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>1500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>2500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>1800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>1400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>400</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1004,8 +1031,14 @@
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1063,8 +1096,14 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1122,19 +1161,25 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
-        <v>0</v>
+      <c r="D15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F15" s="3" t="s">
-        <v>3</v>
+      <c r="F15" s="3">
+        <v>0</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>3</v>
@@ -1148,11 +1193,11 @@
       <c r="J15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3">
-        <v>0</v>
+      <c r="K15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1181,8 +1226,14 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1201,56 +1252,58 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E17" s="3">
+        <v>4400</v>
+      </c>
+      <c r="F17" s="3">
         <v>4900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>7700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>5300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>4600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>4800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>5300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>3300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>3300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>4700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>3600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>2500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>500</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1260,8 +1313,14 @@
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1269,47 +1328,47 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="G18" s="3">
         <v>-7700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-5200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-4600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-4800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-5200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-3300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-3300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-4700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-3500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-2500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-500</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1319,8 +1378,14 @@
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1342,8 +1407,10 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1351,29 +1418,29 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F20" s="3">
+        <v>200</v>
+      </c>
+      <c r="G20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>100</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
@@ -1384,14 +1451,14 @@
         <v>0</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>-100</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1401,8 +1468,14 @@
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1410,47 +1483,47 @@
         <v>3</v>
       </c>
       <c r="E21" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="G21" s="3">
         <v>-7600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-5100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-4600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-4500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-5100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-3300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-3200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-4700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-3600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-2400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-600</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1460,8 +1533,14 @@
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1519,56 +1598,62 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-4700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="G23" s="3">
         <v>-7700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-5100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-4600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-4600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-5100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-3300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-3200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-4700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-3600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-2400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-600</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1578,8 +1663,14 @@
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1593,14 +1684,14 @@
         <v>0</v>
       </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
         <v>0</v>
       </c>
@@ -1622,11 +1713,11 @@
       <c r="P24" s="3">
         <v>0</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R24" s="3" t="s">
-        <v>3</v>
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
+        <v>0</v>
       </c>
       <c r="S24" s="3" t="s">
         <v>3</v>
@@ -1637,8 +1728,14 @@
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1696,56 +1793,62 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-4700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="G26" s="3">
         <v>-7700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-5100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-4700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-4600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-5100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-3300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-3200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-4700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-3600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-2500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-600</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1755,56 +1858,62 @@
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-4700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="G27" s="3">
         <v>-7700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-5100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-4700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-4600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-5100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-3300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-3200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-4700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-3600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-2500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-600</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1814,8 +1923,14 @@
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1873,8 +1988,14 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1932,8 +2053,14 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1991,8 +2118,14 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2050,8 +2183,14 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2059,29 +2198,29 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>300</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-100</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>-200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
@@ -2092,14 +2231,14 @@
         <v>0</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>100</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2109,56 +2248,62 @@
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-4700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="G33" s="3">
         <v>-7700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-5100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-4700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-4600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-5100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-3300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-3200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-4700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-3600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-2500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-600</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2168,8 +2313,14 @@
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2227,56 +2378,62 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-4700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="G35" s="3">
         <v>-7700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-5100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-4700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-4600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-5100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-3300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-3200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-4700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-3600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-2500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-600</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2286,61 +2443,67 @@
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43921</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2350,8 +2513,14 @@
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2373,8 +2542,10 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2396,50 +2567,52 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E41" s="3">
+        <v>11800</v>
+      </c>
+      <c r="F41" s="3">
         <v>4300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>6300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>6000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>7300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>10900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>14300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>34300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>36900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>43200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>46600</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2455,44 +2628,50 @@
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E42" s="3">
+        <v>5000</v>
+      </c>
+      <c r="F42" s="3">
         <v>8000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>9900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>11800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>12800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>11900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>9900</v>
       </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L42" s="3">
+      <c r="L42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N42" s="3">
         <v>40100</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2505,28 +2684,34 @@
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S42" s="3">
-        <v>0</v>
-      </c>
-      <c r="T42" s="3">
-        <v>0</v>
+      <c r="S42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E43" s="3">
         <v>200</v>
       </c>
       <c r="F43" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G43" s="3">
         <v>200</v>
@@ -2544,19 +2729,19 @@
         <v>200</v>
       </c>
       <c r="L43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M43" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="N43" s="3">
         <v>100</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
+      <c r="O43" s="3">
+        <v>500</v>
+      </c>
+      <c r="P43" s="3">
+        <v>100</v>
       </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
@@ -2573,8 +2758,14 @@
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2632,50 +2823,56 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>700</v>
+      </c>
+      <c r="F45" s="3">
         <v>900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>1000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>1300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>1500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>1400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>1800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>700</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2691,50 +2888,56 @@
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E46" s="3">
+        <v>17800</v>
+      </c>
+      <c r="F46" s="3">
         <v>13200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>17300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>19300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>21100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>24300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>25800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>36400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>37700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>41600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>44300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>47400</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2750,35 +2953,41 @@
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>3</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3">
+        <v>0</v>
       </c>
       <c r="F47" s="3">
+        <v>0</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3">
         <v>1000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>1900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>2900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>4900</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2791,11 +3000,11 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -2809,50 +3018,56 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>700</v>
+      </c>
+      <c r="E48" s="3">
         <v>800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
+        <v>800</v>
+      </c>
+      <c r="G48" s="3">
         <v>900</v>
-      </c>
-      <c r="F48" s="3">
-        <v>1000</v>
-      </c>
-      <c r="G48" s="3">
-        <v>1000</v>
       </c>
       <c r="H48" s="3">
         <v>1000</v>
       </c>
       <c r="I48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K48" s="3">
         <v>1100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>1200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>1200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>600</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2868,8 +3083,14 @@
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2927,8 +3148,14 @@
       <c r="U49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2986,8 +3213,14 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3045,8 +3278,14 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3054,7 +3293,7 @@
         <v>0</v>
       </c>
       <c r="E52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F52" s="3">
         <v>0</v>
@@ -3072,10 +3311,10 @@
         <v>0</v>
       </c>
       <c r="K52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M52" s="3">
         <v>100</v>
@@ -3083,11 +3322,11 @@
       <c r="N52" s="3">
         <v>100</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
+      <c r="O52" s="3">
+        <v>100</v>
+      </c>
+      <c r="P52" s="3">
+        <v>100</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
@@ -3104,8 +3343,14 @@
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3163,50 +3408,56 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>18600</v>
+      </c>
+      <c r="F54" s="3">
         <v>14100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>18300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>21300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>24100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>28300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>31900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>37600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>39000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>42600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>45400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>48000</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3222,8 +3473,14 @@
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3245,8 +3502,10 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3268,8 +3527,10 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3277,41 +3538,41 @@
         <v>1400</v>
       </c>
       <c r="E57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="G57" s="3">
         <v>900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>2200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>1600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>1000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>2100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>1000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>900</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3327,8 +3588,14 @@
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3363,13 +3630,13 @@
         <v>100</v>
       </c>
       <c r="N58" s="3">
-        <v>0</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="O58" s="3">
+        <v>100</v>
+      </c>
+      <c r="P58" s="3">
+        <v>0</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
@@ -3386,50 +3653,56 @@
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E59" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F59" s="3">
         <v>4300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>4600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>2800</v>
-      </c>
-      <c r="G59" s="3">
-        <v>2400</v>
-      </c>
-      <c r="H59" s="3">
-        <v>3200</v>
       </c>
       <c r="I59" s="3">
         <v>2400</v>
       </c>
       <c r="J59" s="3">
+        <v>3200</v>
+      </c>
+      <c r="K59" s="3">
+        <v>2400</v>
+      </c>
+      <c r="L59" s="3">
         <v>2000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>2700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>1400</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3445,50 +3718,56 @@
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>4900</v>
+      </c>
+      <c r="F60" s="3">
         <v>5800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>5600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>5200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>4100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>4300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>3400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>4200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>2600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>3600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>2500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>2300</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3504,8 +3783,14 @@
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3513,10 +3798,10 @@
         <v>400</v>
       </c>
       <c r="E61" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="F61" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="G61" s="3">
         <v>500</v>
@@ -3528,10 +3813,10 @@
         <v>500</v>
       </c>
       <c r="J61" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="K61" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="L61" s="3">
         <v>600</v>
@@ -3540,14 +3825,14 @@
         <v>600</v>
       </c>
       <c r="N61" s="3">
+        <v>600</v>
+      </c>
+      <c r="O61" s="3">
+        <v>600</v>
+      </c>
+      <c r="P61" s="3">
         <v>700</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3563,50 +3848,56 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>500</v>
+      </c>
+      <c r="E62" s="3">
         <v>600</v>
-      </c>
-      <c r="E62" s="3">
-        <v>1100</v>
       </c>
       <c r="F62" s="3">
         <v>600</v>
       </c>
       <c r="G62" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H62" s="3">
         <v>600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
+        <v>600</v>
+      </c>
+      <c r="J62" s="3">
         <v>800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>1000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>1000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>600</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3622,8 +3913,14 @@
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3681,8 +3978,14 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3740,8 +4043,14 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3799,50 +4108,56 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>6000</v>
+      </c>
+      <c r="F66" s="3">
         <v>6800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>7200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>6200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>5200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>5700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>4900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>5800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>4200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>5000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>4000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>3600</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3858,8 +4173,14 @@
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3881,8 +4202,10 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3940,8 +4263,14 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3999,8 +4328,14 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4058,8 +4393,14 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4117,50 +4458,56 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-64800</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-60800</v>
+      </c>
+      <c r="F72" s="3">
         <v>-56100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-51300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-43700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-38500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-33800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-29300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-24200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-20900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-17700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-13000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-9500</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4176,8 +4523,14 @@
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4235,8 +4588,14 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4294,8 +4653,14 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4353,50 +4718,56 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E76" s="3">
+        <v>12600</v>
+      </c>
+      <c r="F76" s="3">
         <v>7300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>11100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>15100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>18900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>22700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>27000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>31800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>34800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>37500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>41400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>44500</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4412,8 +4783,14 @@
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4471,61 +4848,67 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43921</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4535,56 +4918,62 @@
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-4700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="G81" s="3">
         <v>-7700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-5100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-4700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-4600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-5100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-3300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-3200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-4700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-3600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-2500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-600</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4594,8 +4983,14 @@
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4617,8 +5012,10 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4661,11 +5058,11 @@
       <c r="P83" s="3">
         <v>0</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+      <c r="R83" s="3">
+        <v>0</v>
       </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
@@ -4676,8 +5073,14 @@
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4735,8 +5138,14 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4794,8 +5203,14 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4853,8 +5268,14 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4912,8 +5333,14 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4971,56 +5398,62 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="F89" s="3">
         <v>-4000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-5000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-4200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-3900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-3300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-5100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-2400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-4100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-2200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-3200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-2800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-800</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5030,8 +5463,14 @@
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5053,8 +5492,10 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5071,11 +5512,11 @@
         <v>0</v>
       </c>
       <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
         <v>0</v>
       </c>
@@ -5097,11 +5538,11 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
+        <v>0</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>3</v>
@@ -5112,8 +5553,14 @@
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5171,8 +5618,14 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5230,35 +5683,41 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F94" s="3">
         <v>1900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>3000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>2100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>100</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>-14900</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
       <c r="L94" s="3">
         <v>0</v>
       </c>
@@ -5274,11 +5733,11 @@
       <c r="P94" s="3">
         <v>0</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
+        <v>0</v>
       </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
@@ -5289,8 +5748,14 @@
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5312,8 +5777,10 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5371,8 +5838,14 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5430,8 +5903,14 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5489,8 +5968,14 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5548,26 +6033,32 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E100" s="3">
+        <v>9600</v>
+      </c>
+      <c r="F100" s="3">
         <v>100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>2200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>700</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
         <v>0</v>
       </c>
@@ -5581,23 +6072,23 @@
         <v>0</v>
       </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>-200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>42000</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>1400</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5607,41 +6098,47 @@
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E101" s="3">
+        <v>500</v>
+      </c>
+      <c r="F101" s="3">
         <v>-100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>100</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-100</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
         <v>100</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
       <c r="N101" s="3">
         <v>0</v>
       </c>
@@ -5651,11 +6148,11 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R101" s="3" t="s">
-        <v>3</v>
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
+        <v>0</v>
       </c>
       <c r="S101" s="3" t="s">
         <v>3</v>
@@ -5666,56 +6163,62 @@
       <c r="U101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>7500</v>
+      </c>
+      <c r="F102" s="3">
         <v>-2000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-1300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-3600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-3400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-20000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-2500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-4100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-2200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-3400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>39100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>600</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5723,6 +6226,12 @@
         <v>3</v>
       </c>
       <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GANX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GANX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="92">
   <si>
     <t>GANX</t>
   </si>
@@ -656,90 +656,91 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
@@ -752,8 +753,11 @@
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -770,20 +774,20 @@
         <v>0</v>
       </c>
       <c r="H8" s="3">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3">
         <v>100</v>
       </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
       <c r="J8" s="3">
         <v>0</v>
       </c>
       <c r="K8" s="3">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3">
         <v>100</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
-      </c>
       <c r="M8" s="3">
         <v>0</v>
       </c>
@@ -791,19 +795,19 @@
         <v>0</v>
       </c>
       <c r="O8" s="3">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3">
         <v>100</v>
       </c>
-      <c r="P8" s="3">
-        <v>0</v>
-      </c>
       <c r="Q8" s="3">
         <v>0</v>
       </c>
       <c r="R8" s="3">
         <v>0</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
+      <c r="S8" s="3">
+        <v>0</v>
       </c>
       <c r="T8" s="3" t="s">
         <v>3</v>
@@ -811,14 +815,17 @@
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V8" s="3">
-        <v>0</v>
+      <c r="V8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -882,8 +889,11 @@
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -947,8 +957,11 @@
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -972,58 +985,59 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E12" s="3">
         <v>2500</v>
-      </c>
-      <c r="E12" s="3">
-        <v>2400</v>
       </c>
       <c r="F12" s="3">
         <v>2400</v>
       </c>
       <c r="G12" s="3">
+        <v>2400</v>
+      </c>
+      <c r="H12" s="3">
         <v>4000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>2800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>2300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>2000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>2600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>2500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1400</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>400</v>
       </c>
       <c r="R12" s="3">
         <v>400</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>3</v>
+      <c r="S12" s="3">
+        <v>400</v>
       </c>
       <c r="T12" s="3" t="s">
         <v>3</v>
@@ -1037,8 +1051,11 @@
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1102,8 +1119,11 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1167,8 +1187,11 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1178,11 +1201,11 @@
       <c r="E15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F15" s="3">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>3</v>
+      <c r="F15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>3</v>
@@ -1199,8 +1222,8 @@
       <c r="L15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
+      <c r="M15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1232,8 +1255,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1254,58 +1280,59 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>4400</v>
+        <v>8200</v>
       </c>
       <c r="E17" s="3">
         <v>4400</v>
       </c>
       <c r="F17" s="3">
+        <v>4400</v>
+      </c>
+      <c r="G17" s="3">
         <v>4900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>7700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5300</v>
-      </c>
-      <c r="L17" s="3">
-        <v>3300</v>
       </c>
       <c r="M17" s="3">
         <v>3300</v>
       </c>
       <c r="N17" s="3">
+        <v>3300</v>
+      </c>
+      <c r="O17" s="3">
         <v>4700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2500</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>500</v>
       </c>
       <c r="R17" s="3">
         <v>500</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
+      <c r="S17" s="3">
+        <v>500</v>
       </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
@@ -1319,8 +1346,11 @@
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1331,46 +1361,46 @@
         <v>-4400</v>
       </c>
       <c r="F18" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="G18" s="3">
         <v>-4900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-7700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-5200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-4600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-4800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-5200</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-3300</v>
       </c>
       <c r="M18" s="3">
         <v>-3300</v>
       </c>
       <c r="N18" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="O18" s="3">
         <v>-4700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-3500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2500</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>-500</v>
       </c>
       <c r="R18" s="3">
         <v>-500</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
+      <c r="S18" s="3">
+        <v>-500</v>
       </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
@@ -1384,8 +1414,11 @@
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1409,8 +1442,9 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1418,31 +1452,31 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>400</v>
+      </c>
+      <c r="F20" s="3">
         <v>-300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>200</v>
-      </c>
-      <c r="G20" s="3">
-        <v>100</v>
       </c>
       <c r="H20" s="3">
         <v>100</v>
       </c>
       <c r="I20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>200</v>
-      </c>
-      <c r="K20" s="3">
-        <v>100</v>
       </c>
       <c r="L20" s="3">
         <v>100</v>
       </c>
       <c r="M20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N20" s="3">
         <v>0</v>
@@ -1457,11 +1491,11 @@
         <v>0</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>-100</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1474,8 +1508,11 @@
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1483,50 +1520,50 @@
         <v>3</v>
       </c>
       <c r="E21" s="3">
-        <v>-4700</v>
+        <v>-4000</v>
       </c>
       <c r="F21" s="3">
         <v>-4700</v>
       </c>
       <c r="G21" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="H21" s="3">
         <v>-7600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-5100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-4600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-4500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-5100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-3300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-3200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-4700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-3600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-600</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1539,8 +1576,11 @@
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1604,59 +1644,62 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-4000</v>
-      </c>
-      <c r="E23" s="3">
-        <v>-4700</v>
       </c>
       <c r="F23" s="3">
         <v>-4700</v>
       </c>
       <c r="G23" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="H23" s="3">
         <v>-7700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-5100</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-4600</v>
       </c>
       <c r="J23" s="3">
         <v>-4600</v>
       </c>
       <c r="K23" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="L23" s="3">
         <v>-5100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-3300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-3200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-4700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-3600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-600</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1669,8 +1712,11 @@
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1690,11 +1736,11 @@
         <v>0</v>
       </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
         <v>0</v>
       </c>
@@ -1719,8 +1765,8 @@
       <c r="R24" s="3">
         <v>0</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
+      <c r="S24" s="3">
+        <v>0</v>
       </c>
       <c r="T24" s="3" t="s">
         <v>3</v>
@@ -1734,8 +1780,11 @@
       <c r="W24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1799,59 +1848,62 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-4000</v>
-      </c>
-      <c r="E26" s="3">
-        <v>-4700</v>
       </c>
       <c r="F26" s="3">
         <v>-4700</v>
       </c>
       <c r="G26" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="H26" s="3">
         <v>-7700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-5100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-4700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-4600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-5100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-3300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-3200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-4700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-3600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-600</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1864,59 +1916,62 @@
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-4000</v>
-      </c>
-      <c r="E27" s="3">
-        <v>-4700</v>
       </c>
       <c r="F27" s="3">
         <v>-4700</v>
       </c>
       <c r="G27" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="H27" s="3">
         <v>-7700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-5100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-4700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-4600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-5100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-3300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-3200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-4700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-3600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-600</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1929,8 +1984,11 @@
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1994,8 +2052,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2059,8 +2120,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2124,8 +2188,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2189,8 +2256,11 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2198,31 +2268,31 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F32" s="3">
         <v>300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-200</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-100</v>
       </c>
       <c r="H32" s="3">
         <v>-100</v>
       </c>
       <c r="I32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-200</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-100</v>
       </c>
       <c r="L32" s="3">
         <v>-100</v>
       </c>
       <c r="M32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N32" s="3">
         <v>0</v>
@@ -2237,11 +2307,11 @@
         <v>0</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>100</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2254,59 +2324,62 @@
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-4000</v>
-      </c>
-      <c r="E33" s="3">
-        <v>-4700</v>
       </c>
       <c r="F33" s="3">
         <v>-4700</v>
       </c>
       <c r="G33" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="H33" s="3">
         <v>-7700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-5100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-4700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-4600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-5100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-3300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-3200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-4700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-3600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-600</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2319,8 +2392,11 @@
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2384,59 +2460,62 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-4000</v>
-      </c>
-      <c r="E35" s="3">
-        <v>-4700</v>
       </c>
       <c r="F35" s="3">
         <v>-4700</v>
       </c>
       <c r="G35" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="H35" s="3">
         <v>-7700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-5100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-4700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-4600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-5100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-3300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-3200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-4700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-3600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-600</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2449,64 +2528,67 @@
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2519,8 +2601,11 @@
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2544,8 +2629,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2569,53 +2655,54 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>16900</v>
+      </c>
+      <c r="E41" s="3">
         <v>10600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>11800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>7300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>10900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>14300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>34300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>36900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>43200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>46600</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2634,47 +2721,50 @@
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>2000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>5000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>8000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>9900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>11800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>12800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>11900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>9900</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N42" s="3">
+      <c r="N42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O42" s="3">
         <v>40100</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2690,8 +2780,8 @@
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U42" s="3">
-        <v>0</v>
+      <c r="U42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V42" s="3">
         <v>0</v>
@@ -2699,22 +2789,25 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E43" s="3">
         <v>200</v>
       </c>
       <c r="F43" s="3">
+        <v>200</v>
+      </c>
+      <c r="G43" s="3">
         <v>100</v>
-      </c>
-      <c r="G43" s="3">
-        <v>200</v>
       </c>
       <c r="H43" s="3">
         <v>200</v>
@@ -2735,17 +2828,17 @@
         <v>200</v>
       </c>
       <c r="N43" s="3">
+        <v>200</v>
+      </c>
+      <c r="O43" s="3">
         <v>100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>100</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2764,8 +2857,11 @@
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2829,52 +2925,55 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E45" s="3">
         <v>1000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>500</v>
-      </c>
-      <c r="O45" s="3">
-        <v>700</v>
       </c>
       <c r="P45" s="3">
         <v>700</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
+      <c r="Q45" s="3">
+        <v>700</v>
       </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
@@ -2894,53 +2993,56 @@
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>18500</v>
+      </c>
+      <c r="E46" s="3">
         <v>13900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>17800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>13200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>17300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>19300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>21100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>24300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>25800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>36400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>37700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>41600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>44300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>47400</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2959,38 +3061,41 @@
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E47" s="3">
-        <v>0</v>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F47" s="3">
         <v>0</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H47" s="3">
+      <c r="G47" s="3">
+        <v>0</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3">
         <v>1000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>4900</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3006,8 +3111,8 @@
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R47" s="3">
-        <v>0</v>
+      <c r="R47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S47" s="3">
         <v>0</v>
@@ -3024,25 +3129,28 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="E48" s="3">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="F48" s="3">
         <v>800</v>
       </c>
       <c r="G48" s="3">
+        <v>800</v>
+      </c>
+      <c r="H48" s="3">
         <v>900</v>
-      </c>
-      <c r="H48" s="3">
-        <v>1000</v>
       </c>
       <c r="I48" s="3">
         <v>1000</v>
@@ -3051,26 +3159,26 @@
         <v>1000</v>
       </c>
       <c r="K48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="L48" s="3">
         <v>1100</v>
-      </c>
-      <c r="L48" s="3">
-        <v>1200</v>
       </c>
       <c r="M48" s="3">
         <v>1200</v>
       </c>
       <c r="N48" s="3">
-        <v>900</v>
+        <v>1200</v>
       </c>
       <c r="O48" s="3">
         <v>900</v>
       </c>
       <c r="P48" s="3">
+        <v>900</v>
+      </c>
+      <c r="Q48" s="3">
         <v>600</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3089,31 +3197,34 @@
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E49" s="3">
-        <v>0</v>
-      </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3">
-        <v>0</v>
+        <v>200</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K49" s="3">
         <v>0</v>
@@ -3154,8 +3265,11 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3219,8 +3333,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3284,8 +3401,11 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3293,11 +3413,11 @@
         <v>0</v>
       </c>
       <c r="E52" s="3">
+        <v>0</v>
+      </c>
+      <c r="F52" s="3">
         <v>100</v>
       </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
       <c r="G52" s="3">
         <v>0</v>
       </c>
@@ -3317,7 +3437,7 @@
         <v>0</v>
       </c>
       <c r="M52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N52" s="3">
         <v>100</v>
@@ -3328,8 +3448,8 @@
       <c r="P52" s="3">
         <v>100</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
+      <c r="Q52" s="3">
+        <v>100</v>
       </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
@@ -3349,8 +3469,11 @@
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3414,53 +3537,56 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>19200</v>
+      </c>
+      <c r="E54" s="3">
         <v>14600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>18600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>14100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>18300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>21300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>24100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>28300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>31900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>37600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>39000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>42600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>45400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>48000</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3479,8 +3605,11 @@
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3504,8 +3633,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3529,53 +3659,54 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>900</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3594,8 +3725,11 @@
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3636,10 +3770,10 @@
         <v>100</v>
       </c>
       <c r="P58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>0</v>
       </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
@@ -3659,52 +3793,55 @@
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3500</v>
+        <v>4400</v>
       </c>
       <c r="E59" s="3">
         <v>3500</v>
       </c>
       <c r="F59" s="3">
+        <v>3500</v>
+      </c>
+      <c r="G59" s="3">
         <v>4300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2700</v>
-      </c>
-      <c r="O59" s="3">
-        <v>1400</v>
       </c>
       <c r="P59" s="3">
         <v>1400</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
+      <c r="Q59" s="3">
+        <v>1400</v>
       </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
@@ -3724,53 +3861,56 @@
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E60" s="3">
         <v>5000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2300</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3789,8 +3929,11 @@
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3804,7 +3947,7 @@
         <v>400</v>
       </c>
       <c r="G61" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="H61" s="3">
         <v>500</v>
@@ -3819,7 +3962,7 @@
         <v>500</v>
       </c>
       <c r="L61" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="M61" s="3">
         <v>600</v>
@@ -3831,11 +3974,11 @@
         <v>600</v>
       </c>
       <c r="P61" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q61" s="3">
         <v>700</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3854,8 +3997,11 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3863,44 +4009,44 @@
         <v>500</v>
       </c>
       <c r="E62" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="F62" s="3">
         <v>600</v>
       </c>
       <c r="G62" s="3">
+        <v>600</v>
+      </c>
+      <c r="H62" s="3">
         <v>1100</v>
-      </c>
-      <c r="H62" s="3">
-        <v>600</v>
       </c>
       <c r="I62" s="3">
         <v>600</v>
       </c>
       <c r="J62" s="3">
+        <v>600</v>
+      </c>
+      <c r="K62" s="3">
         <v>800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>900</v>
-      </c>
-      <c r="L62" s="3">
-        <v>1000</v>
       </c>
       <c r="M62" s="3">
         <v>1000</v>
       </c>
       <c r="N62" s="3">
+        <v>1000</v>
+      </c>
+      <c r="O62" s="3">
         <v>800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>600</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3919,8 +4065,11 @@
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3984,8 +4133,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4049,8 +4201,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4114,53 +4269,56 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E66" s="3">
         <v>5900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3600</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4179,8 +4337,11 @@
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4204,8 +4365,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4269,8 +4431,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4334,8 +4499,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4399,8 +4567,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4464,53 +4635,56 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-72900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-64800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-60800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-56100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-51300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-43700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-38500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-33800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-29300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-24200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-20900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-17700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-13000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-9500</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4529,8 +4703,11 @@
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4594,8 +4771,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4659,8 +4839,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4724,53 +4907,56 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E76" s="3">
         <v>8600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>12600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>11100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>15100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>18900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>22700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>27000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>31800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>34800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>37500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>41400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>44500</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4789,8 +4975,11 @@
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4854,64 +5043,67 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4924,59 +5116,62 @@
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-4000</v>
-      </c>
-      <c r="E81" s="3">
-        <v>-4700</v>
       </c>
       <c r="F81" s="3">
         <v>-4700</v>
       </c>
       <c r="G81" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="H81" s="3">
         <v>-7700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-5100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-4700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-4600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-5100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-3300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-3200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-4700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-3600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-600</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4989,8 +5184,11 @@
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5014,8 +5212,9 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5064,8 +5263,8 @@
       <c r="R83" s="3">
         <v>0</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
+      <c r="S83" s="3">
+        <v>0</v>
       </c>
       <c r="T83" s="3" t="s">
         <v>3</v>
@@ -5079,8 +5278,11 @@
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5144,8 +5346,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5209,8 +5414,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5274,8 +5482,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5339,8 +5550,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5404,59 +5618,62 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-3600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-5700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-4000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-5000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-4200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-3900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-3300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-5100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-4100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-3200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-800</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5469,8 +5686,11 @@
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5494,8 +5714,9 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5515,11 +5736,11 @@
         <v>0</v>
       </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
         <v>0</v>
       </c>
@@ -5544,8 +5765,8 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
@@ -5559,8 +5780,11 @@
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5624,8 +5848,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5689,38 +5916,41 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E94" s="3">
         <v>3000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>3100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>1900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>3000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>2100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>100</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
       <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>-14900</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
         <v>0</v>
       </c>
@@ -5739,8 +5969,8 @@
       <c r="R94" s="3">
         <v>0</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
+      <c r="S94" s="3">
+        <v>0</v>
       </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
@@ -5754,8 +5984,11 @@
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5779,8 +6012,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5844,8 +6078,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5909,8 +6146,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5974,8 +6214,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6039,29 +6282,32 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>9600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>700</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
         <v>0</v>
       </c>
@@ -6078,20 +6324,20 @@
         <v>0</v>
       </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>-200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>42000</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>1400</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6104,44 +6350,47 @@
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
         <v>-400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>100</v>
       </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
       <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
         <v>200</v>
-      </c>
-      <c r="J101" s="3">
-        <v>-100</v>
       </c>
       <c r="K101" s="3">
         <v>-100</v>
       </c>
       <c r="L101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>100</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
       <c r="O101" s="3">
         <v>0</v>
       </c>
@@ -6154,8 +6403,8 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>3</v>
+      <c r="S101" s="3">
+        <v>0</v>
       </c>
       <c r="T101" s="3" t="s">
         <v>3</v>
@@ -6169,59 +6418,62 @@
       <c r="W101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>7500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-3600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-3400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-20000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-4100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>39100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>600</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6232,6 +6484,9 @@
         <v>3</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GANX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GANX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="92">
   <si>
     <t>GANX</t>
   </si>
@@ -656,94 +656,95 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
@@ -756,41 +757,44 @@
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
+      <c r="E8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>
       </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3">
         <v>100</v>
       </c>
-      <c r="J8" s="3">
-        <v>0</v>
-      </c>
       <c r="K8" s="3">
         <v>0</v>
       </c>
       <c r="L8" s="3">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3">
         <v>100</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
-      </c>
       <c r="N8" s="3">
         <v>0</v>
       </c>
@@ -798,19 +802,19 @@
         <v>0</v>
       </c>
       <c r="P8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3">
         <v>100</v>
       </c>
-      <c r="Q8" s="3">
-        <v>0</v>
-      </c>
       <c r="R8" s="3">
         <v>0</v>
       </c>
       <c r="S8" s="3">
         <v>0</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
+      <c r="T8" s="3">
+        <v>0</v>
       </c>
       <c r="U8" s="3" t="s">
         <v>3</v>
@@ -818,37 +822,40 @@
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W8" s="3">
-        <v>0</v>
+      <c r="W8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
+      <c r="D9" s="3">
+        <v>300</v>
+      </c>
+      <c r="E9" s="3">
+        <v>300</v>
+      </c>
+      <c r="F9" s="3">
+        <v>2500</v>
+      </c>
+      <c r="G9" s="3">
+        <v>2200</v>
+      </c>
+      <c r="H9" s="3">
+        <v>300</v>
+      </c>
+      <c r="I9" s="3">
+        <v>200</v>
+      </c>
+      <c r="J9" s="3">
+        <v>2800</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
@@ -892,31 +899,34 @@
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E10" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F10" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="G10" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="H10" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I10" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J10" s="3">
+        <v>-2700</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -960,8 +970,11 @@
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -986,61 +999,62 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>4400</v>
+        <v>2300</v>
       </c>
       <c r="E12" s="3">
+        <v>4200</v>
+      </c>
+      <c r="F12" s="3">
+        <v>2700</v>
+      </c>
+      <c r="G12" s="3">
+        <v>2800</v>
+      </c>
+      <c r="H12" s="3">
+        <v>2100</v>
+      </c>
+      <c r="I12" s="3">
+        <v>3700</v>
+      </c>
+      <c r="J12" s="3">
+        <v>2800</v>
+      </c>
+      <c r="K12" s="3">
+        <v>2300</v>
+      </c>
+      <c r="L12" s="3">
+        <v>2000</v>
+      </c>
+      <c r="M12" s="3">
+        <v>2600</v>
+      </c>
+      <c r="N12" s="3">
+        <v>1600</v>
+      </c>
+      <c r="O12" s="3">
+        <v>1500</v>
+      </c>
+      <c r="P12" s="3">
         <v>2500</v>
       </c>
-      <c r="F12" s="3">
-        <v>2400</v>
-      </c>
-      <c r="G12" s="3">
-        <v>2400</v>
-      </c>
-      <c r="H12" s="3">
-        <v>4000</v>
-      </c>
-      <c r="I12" s="3">
-        <v>2800</v>
-      </c>
-      <c r="J12" s="3">
-        <v>2300</v>
-      </c>
-      <c r="K12" s="3">
-        <v>2000</v>
-      </c>
-      <c r="L12" s="3">
-        <v>2600</v>
-      </c>
-      <c r="M12" s="3">
-        <v>1600</v>
-      </c>
-      <c r="N12" s="3">
-        <v>1500</v>
-      </c>
-      <c r="O12" s="3">
-        <v>2500</v>
-      </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1400</v>
-      </c>
-      <c r="R12" s="3">
-        <v>400</v>
       </c>
       <c r="S12" s="3">
         <v>400</v>
       </c>
-      <c r="T12" s="3" t="s">
-        <v>3</v>
+      <c r="T12" s="3">
+        <v>400</v>
       </c>
       <c r="U12" s="3" t="s">
         <v>3</v>
@@ -1054,8 +1068,11 @@
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1122,31 +1139,34 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1190,31 +1210,34 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>3</v>
+      <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
       </c>
       <c r="G15" s="3">
         <v>0</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>3</v>
+      <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
+        <v>0</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>3</v>
@@ -1225,8 +1248,8 @@
       <c r="M15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N15" s="3">
-        <v>0</v>
+      <c r="N15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O15" s="3">
         <v>0</v>
@@ -1258,8 +1281,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1281,61 +1307,62 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E17" s="3">
         <v>8200</v>
-      </c>
-      <c r="E17" s="3">
-        <v>4400</v>
       </c>
       <c r="F17" s="3">
         <v>4400</v>
       </c>
       <c r="G17" s="3">
+        <v>4400</v>
+      </c>
+      <c r="H17" s="3">
         <v>4900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>7700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5300</v>
-      </c>
-      <c r="M17" s="3">
-        <v>3300</v>
       </c>
       <c r="N17" s="3">
         <v>3300</v>
       </c>
       <c r="O17" s="3">
+        <v>3300</v>
+      </c>
+      <c r="P17" s="3">
         <v>4700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2500</v>
-      </c>
-      <c r="R17" s="3">
-        <v>500</v>
       </c>
       <c r="S17" s="3">
         <v>500</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
+      <c r="T17" s="3">
+        <v>500</v>
       </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
@@ -1349,61 +1376,64 @@
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-4500</v>
       </c>
       <c r="E18" s="3">
-        <v>-4400</v>
+        <v>-8200</v>
       </c>
       <c r="F18" s="3">
         <v>-4400</v>
       </c>
       <c r="G18" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="H18" s="3">
         <v>-4900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-7700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-5200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-4600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-4800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-5200</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-3300</v>
       </c>
       <c r="N18" s="3">
         <v>-3300</v>
       </c>
       <c r="O18" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="P18" s="3">
         <v>-4700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-2500</v>
-      </c>
-      <c r="R18" s="3">
-        <v>-500</v>
       </c>
       <c r="S18" s="3">
         <v>-500</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
+      <c r="T18" s="3">
+        <v>-500</v>
       </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
@@ -1417,8 +1447,11 @@
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1443,25 +1476,26 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>100</v>
       </c>
       <c r="E20" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3">
         <v>-300</v>
       </c>
       <c r="G20" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="H20" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="I20" s="3">
         <v>100</v>
@@ -1470,16 +1504,16 @@
         <v>0</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>200</v>
-      </c>
-      <c r="L20" s="3">
-        <v>100</v>
       </c>
       <c r="M20" s="3">
         <v>100</v>
       </c>
       <c r="N20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O20" s="3">
         <v>0</v>
@@ -1494,11 +1528,11 @@
         <v>0</v>
       </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>-100</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1511,62 +1545,65 @@
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-4600</v>
       </c>
       <c r="E21" s="3">
-        <v>-4000</v>
+        <v>-8200</v>
       </c>
       <c r="F21" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="K21" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="L21" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="M21" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="N21" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="O21" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="P21" s="3">
         <v>-4700</v>
       </c>
-      <c r="G21" s="3">
-        <v>-4700</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-7600</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-5100</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-4600</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="L21" s="3">
-        <v>-5100</v>
-      </c>
-      <c r="M21" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="N21" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="O21" s="3">
-        <v>-4700</v>
-      </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-2400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-600</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1579,31 +1616,34 @@
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1647,62 +1687,65 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-8100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-4000</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-4700</v>
       </c>
       <c r="G23" s="3">
         <v>-4700</v>
       </c>
       <c r="H23" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="I23" s="3">
         <v>-7700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-5100</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-4600</v>
       </c>
       <c r="K23" s="3">
         <v>-4600</v>
       </c>
       <c r="L23" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="M23" s="3">
         <v>-5100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-3300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-3200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-4700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-600</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1715,8 +1758,11 @@
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1739,11 +1785,11 @@
         <v>0</v>
       </c>
       <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
         <v>0</v>
       </c>
@@ -1768,8 +1814,8 @@
       <c r="S24" s="3">
         <v>0</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
+      <c r="T24" s="3">
+        <v>0</v>
       </c>
       <c r="U24" s="3" t="s">
         <v>3</v>
@@ -1783,8 +1829,11 @@
       <c r="X24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1851,62 +1900,65 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-8100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-4000</v>
-      </c>
-      <c r="F26" s="3">
-        <v>-4700</v>
       </c>
       <c r="G26" s="3">
         <v>-4700</v>
       </c>
       <c r="H26" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="I26" s="3">
         <v>-7700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-5100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-4700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-4600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-5100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-3300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-3200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-4700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-600</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1919,62 +1971,65 @@
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-8100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-4000</v>
-      </c>
-      <c r="F27" s="3">
-        <v>-4700</v>
       </c>
       <c r="G27" s="3">
         <v>-4700</v>
       </c>
       <c r="H27" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="I27" s="3">
         <v>-7700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-5100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-4700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-4600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-5100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-3300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-3200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-4700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-600</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1987,8 +2042,11 @@
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2055,8 +2113,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2123,8 +2184,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2191,8 +2255,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2259,25 +2326,28 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>-100</v>
       </c>
       <c r="E32" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="F32" s="3">
         <v>300</v>
       </c>
       <c r="G32" s="3">
-        <v>-200</v>
+        <v>-400</v>
       </c>
       <c r="H32" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="I32" s="3">
         <v>-100</v>
@@ -2286,16 +2356,16 @@
         <v>0</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-200</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-100</v>
       </c>
       <c r="M32" s="3">
         <v>-100</v>
       </c>
       <c r="N32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O32" s="3">
         <v>0</v>
@@ -2310,11 +2380,11 @@
         <v>0</v>
       </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>100</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2327,62 +2397,65 @@
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-8100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-4000</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-4700</v>
       </c>
       <c r="G33" s="3">
         <v>-4700</v>
       </c>
       <c r="H33" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="I33" s="3">
         <v>-7700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-5100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-4700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-4600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-5100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-3300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-3200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-4700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-600</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2395,8 +2468,11 @@
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2463,62 +2539,65 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-8100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-4000</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-4700</v>
       </c>
       <c r="G35" s="3">
         <v>-4700</v>
       </c>
       <c r="H35" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="I35" s="3">
         <v>-7700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-5100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-4700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-4600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-5100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-3300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-3200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-4700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-600</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2531,67 +2610,70 @@
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2604,8 +2686,11 @@
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2630,8 +2715,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2656,56 +2742,57 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E41" s="3">
         <v>16900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>10600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>11800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>7300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>10900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>14300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>34300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>36900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>43200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>46600</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2724,8 +2811,11 @@
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2733,41 +2823,41 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>2000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>5000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>8000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>9900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>11800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>12800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>11900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>9900</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O42" s="3">
+      <c r="O42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P42" s="3">
         <v>40100</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2783,8 +2873,8 @@
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V42" s="3">
-        <v>0</v>
+      <c r="V42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W42" s="3">
         <v>0</v>
@@ -2792,25 +2882,28 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>400</v>
+      </c>
+      <c r="E43" s="3">
         <v>300</v>
-      </c>
-      <c r="E43" s="3">
-        <v>200</v>
       </c>
       <c r="F43" s="3">
         <v>200</v>
       </c>
       <c r="G43" s="3">
+        <v>200</v>
+      </c>
+      <c r="H43" s="3">
         <v>100</v>
-      </c>
-      <c r="H43" s="3">
-        <v>200</v>
       </c>
       <c r="I43" s="3">
         <v>200</v>
@@ -2831,17 +2924,17 @@
         <v>200</v>
       </c>
       <c r="O43" s="3">
+        <v>200</v>
+      </c>
+      <c r="P43" s="3">
         <v>100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>100</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2860,31 +2953,34 @@
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2928,55 +3024,58 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>1300</v>
-      </c>
-      <c r="E45" s="3">
-        <v>1000</v>
-      </c>
-      <c r="F45" s="3">
-        <v>700</v>
-      </c>
-      <c r="G45" s="3">
-        <v>900</v>
-      </c>
-      <c r="H45" s="3">
-        <v>1000</v>
-      </c>
-      <c r="I45" s="3">
-        <v>1300</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
         <v>800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>500</v>
-      </c>
-      <c r="P45" s="3">
-        <v>700</v>
       </c>
       <c r="Q45" s="3">
         <v>700</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
+      <c r="R45" s="3">
+        <v>700</v>
       </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
@@ -2996,56 +3095,59 @@
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>13700</v>
+      </c>
+      <c r="E46" s="3">
         <v>18500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>13900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>17800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>13200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>17300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>19300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>21100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>24300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>25800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>36400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>37700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>41600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>44300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>47400</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3064,8 +3166,11 @@
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3075,30 +3180,30 @@
       <c r="E47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I47" s="3">
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3">
         <v>1000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>4900</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3114,8 +3219,8 @@
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S47" s="3">
-        <v>0</v>
+      <c r="S47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T47" s="3">
         <v>0</v>
@@ -3132,8 +3237,11 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3141,47 +3249,47 @@
         <v>400</v>
       </c>
       <c r="E48" s="3">
+        <v>400</v>
+      </c>
+      <c r="F48" s="3">
         <v>500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
+        <v>600</v>
+      </c>
+      <c r="H48" s="3">
+        <v>600</v>
+      </c>
+      <c r="I48" s="3">
+        <v>700</v>
+      </c>
+      <c r="J48" s="3">
         <v>800</v>
-      </c>
-      <c r="G48" s="3">
-        <v>800</v>
-      </c>
-      <c r="H48" s="3">
-        <v>900</v>
-      </c>
-      <c r="I48" s="3">
-        <v>1000</v>
-      </c>
-      <c r="J48" s="3">
-        <v>1000</v>
       </c>
       <c r="K48" s="3">
         <v>1000</v>
       </c>
       <c r="L48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="M48" s="3">
         <v>1100</v>
-      </c>
-      <c r="M48" s="3">
-        <v>1200</v>
       </c>
       <c r="N48" s="3">
         <v>1200</v>
       </c>
       <c r="O48" s="3">
-        <v>900</v>
+        <v>1200</v>
       </c>
       <c r="P48" s="3">
         <v>900</v>
       </c>
       <c r="Q48" s="3">
+        <v>900</v>
+      </c>
+      <c r="R48" s="3">
         <v>600</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3200,8 +3308,11 @@
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3211,23 +3322,23 @@
       <c r="E49" s="3">
         <v>200</v>
       </c>
-      <c r="F49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K49" s="3">
-        <v>0</v>
+      <c r="F49" s="3">
+        <v>200</v>
+      </c>
+      <c r="G49" s="3">
+        <v>200</v>
+      </c>
+      <c r="H49" s="3">
+        <v>200</v>
+      </c>
+      <c r="I49" s="3">
+        <v>200</v>
+      </c>
+      <c r="J49" s="3">
+        <v>200</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L49" s="3">
         <v>0</v>
@@ -3268,8 +3379,11 @@
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3336,8 +3450,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3404,23 +3521,26 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E52" s="3">
         <v>0</v>
       </c>
       <c r="F52" s="3">
+        <v>0</v>
+      </c>
+      <c r="G52" s="3">
         <v>100</v>
       </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
       <c r="H52" s="3">
         <v>0</v>
       </c>
@@ -3440,7 +3560,7 @@
         <v>0</v>
       </c>
       <c r="N52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O52" s="3">
         <v>100</v>
@@ -3451,8 +3571,8 @@
       <c r="Q52" s="3">
         <v>100</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
+      <c r="R52" s="3">
+        <v>100</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
@@ -3472,8 +3592,11 @@
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3540,56 +3663,59 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>14400</v>
+      </c>
+      <c r="E54" s="3">
         <v>19200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>14600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>18600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>14100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>18300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>21300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>24100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>28300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>31900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>37600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>39000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>42600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>45400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>48000</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3608,8 +3734,11 @@
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3634,8 +3763,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3660,56 +3790,57 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E57" s="3">
         <v>2000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>900</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3728,31 +3859,34 @@
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="E58" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F58" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="G58" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="H58" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="I58" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="J58" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="K58" s="3">
         <v>100</v>
@@ -3773,10 +3907,10 @@
         <v>100</v>
       </c>
       <c r="Q58" s="3">
-        <v>0</v>
-      </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="R58" s="3">
+        <v>0</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
@@ -3796,55 +3930,58 @@
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4400</v>
+        <v>700</v>
       </c>
       <c r="E59" s="3">
-        <v>3500</v>
+        <v>800</v>
       </c>
       <c r="F59" s="3">
-        <v>3500</v>
+        <v>1000</v>
       </c>
       <c r="G59" s="3">
-        <v>4300</v>
+        <v>1200</v>
       </c>
       <c r="H59" s="3">
-        <v>4600</v>
+        <v>1400</v>
       </c>
       <c r="I59" s="3">
-        <v>2800</v>
+        <v>1300</v>
       </c>
       <c r="J59" s="3">
+        <v>100</v>
+      </c>
+      <c r="K59" s="3">
         <v>2400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2700</v>
-      </c>
-      <c r="P59" s="3">
-        <v>1400</v>
       </c>
       <c r="Q59" s="3">
         <v>1400</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
+      <c r="R59" s="3">
+        <v>1400</v>
       </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
@@ -3864,56 +4001,59 @@
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E60" s="3">
         <v>6500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2300</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3932,31 +4072,34 @@
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="E61" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="F61" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="G61" s="3">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="H61" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="I61" s="3">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="J61" s="3">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="K61" s="3">
         <v>500</v>
@@ -3965,7 +4108,7 @@
         <v>500</v>
       </c>
       <c r="M61" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="N61" s="3">
         <v>600</v>
@@ -3977,11 +4120,11 @@
         <v>600</v>
       </c>
       <c r="Q61" s="3">
+        <v>600</v>
+      </c>
+      <c r="R61" s="3">
         <v>700</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -4000,56 +4143,59 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>500</v>
-      </c>
-      <c r="E62" s="3">
-        <v>500</v>
-      </c>
-      <c r="F62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K62" s="3">
         <v>600</v>
       </c>
-      <c r="G62" s="3">
-        <v>600</v>
-      </c>
-      <c r="H62" s="3">
-        <v>1100</v>
-      </c>
-      <c r="I62" s="3">
-        <v>600</v>
-      </c>
-      <c r="J62" s="3">
-        <v>600</v>
-      </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>900</v>
-      </c>
-      <c r="M62" s="3">
-        <v>1000</v>
       </c>
       <c r="N62" s="3">
         <v>1000</v>
       </c>
       <c r="O62" s="3">
+        <v>1000</v>
+      </c>
+      <c r="P62" s="3">
         <v>800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>600</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4068,8 +4214,11 @@
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4136,8 +4285,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4204,8 +4356,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4272,56 +4427,59 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E66" s="3">
         <v>7400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3600</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4340,8 +4498,11 @@
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4366,8 +4527,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4434,8 +4596,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4502,8 +4667,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4570,8 +4738,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4638,56 +4809,59 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-77400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-72900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-64800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-60800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-56100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-51300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-43700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-38500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-33800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-29300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-24200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-20900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-17700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-13000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-9500</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4706,8 +4880,11 @@
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4774,8 +4951,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4842,8 +5022,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4910,56 +5093,59 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E76" s="3">
         <v>11800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>12600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>11100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>15100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>18900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>22700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>27000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>31800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>34800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>37500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>41400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>44500</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4978,8 +5164,11 @@
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5046,67 +5235,70 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5119,62 +5311,65 @@
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-8100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-4000</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-4700</v>
       </c>
       <c r="G81" s="3">
         <v>-4700</v>
       </c>
       <c r="H81" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="I81" s="3">
         <v>-7700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-5100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-4700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-4600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-5100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-3300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-3200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-4700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-600</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5187,8 +5382,11 @@
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5213,8 +5411,9 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5266,8 +5465,8 @@
       <c r="S83" s="3">
         <v>0</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
+      <c r="T83" s="3">
+        <v>0</v>
       </c>
       <c r="U83" s="3" t="s">
         <v>3</v>
@@ -5281,8 +5480,11 @@
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5349,8 +5551,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5417,8 +5622,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5485,8 +5693,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5553,8 +5764,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5621,62 +5835,65 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-5800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-3600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-5700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-4000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-5000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-4200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-3900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-3300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-5100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-4100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-2200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-800</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5689,8 +5906,11 @@
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5715,8 +5935,9 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5726,8 +5947,8 @@
       <c r="E91" s="3">
         <v>0</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G91" s="3">
         <v>0</v>
@@ -5739,11 +5960,11 @@
         <v>0</v>
       </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
@@ -5768,8 +5989,8 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
+      <c r="T91" s="3">
+        <v>0</v>
       </c>
       <c r="U91" s="3" t="s">
         <v>3</v>
@@ -5783,8 +6004,11 @@
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5851,8 +6075,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5919,41 +6146,44 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
         <v>2000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>3000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>3100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>1900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>3000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>2100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>100</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-14900</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
         <v>0</v>
       </c>
@@ -5972,8 +6202,8 @@
       <c r="S94" s="3">
         <v>0</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
+      <c r="T94" s="3">
+        <v>0</v>
       </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
@@ -5987,8 +6217,11 @@
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6013,31 +6246,32 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6081,8 +6315,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6149,8 +6386,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6217,8 +6457,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6285,32 +6528,35 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>800</v>
+      </c>
+      <c r="E100" s="3">
         <v>10000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>9600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>700</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
         <v>0</v>
       </c>
@@ -6327,20 +6573,20 @@
         <v>0</v>
       </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>42000</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>1400</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6353,47 +6599,50 @@
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E101" s="3">
-        <v>-400</v>
+        <v>100</v>
       </c>
       <c r="F101" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="G101" s="3">
+        <v>200</v>
+      </c>
+      <c r="H101" s="3">
         <v>-100</v>
       </c>
-      <c r="H101" s="3">
-        <v>100</v>
-      </c>
       <c r="I101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
         <v>200</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-100</v>
       </c>
       <c r="L101" s="3">
         <v>-100</v>
       </c>
       <c r="M101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
         <v>100</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
       <c r="P101" s="3">
         <v>0</v>
       </c>
@@ -6406,8 +6655,8 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>3</v>
+      <c r="T101" s="3">
+        <v>0</v>
       </c>
       <c r="U101" s="3" t="s">
         <v>3</v>
@@ -6421,62 +6670,65 @@
       <c r="X101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E102" s="3">
         <v>6300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>7500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-3600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-3400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-20000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-4100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>39100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>600</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6487,6 +6739,9 @@
         <v>3</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GANX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GANX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="92">
   <si>
     <t>GANX</t>
   </si>
@@ -656,101 +656,102 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
@@ -760,8 +761,14 @@
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -774,95 +781,101 @@
       <c r="F8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G8" s="3">
-        <v>0</v>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="I8" s="3">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L8" s="3">
         <v>100</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
-      </c>
-      <c r="L8" s="3">
-        <v>0</v>
-      </c>
       <c r="M8" s="3">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3">
+        <v>0</v>
+      </c>
+      <c r="O8" s="3">
         <v>100</v>
       </c>
-      <c r="N8" s="3">
-        <v>0</v>
-      </c>
-      <c r="O8" s="3">
-        <v>0</v>
-      </c>
       <c r="P8" s="3">
         <v>0</v>
       </c>
       <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+      <c r="S8" s="3">
         <v>100</v>
       </c>
-      <c r="R8" s="3">
-        <v>0</v>
-      </c>
-      <c r="S8" s="3">
-        <v>0</v>
-      </c>
       <c r="T8" s="3">
         <v>0</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V8" s="3" t="s">
-        <v>3</v>
+      <c r="U8" s="3">
+        <v>0</v>
+      </c>
+      <c r="V8" s="3">
+        <v>0</v>
       </c>
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X8" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="X8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3">
+        <v>9900</v>
+      </c>
+      <c r="F9" s="3">
         <v>300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>2500</v>
       </c>
-      <c r="G9" s="3">
-        <v>2200</v>
-      </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
+        <v>10700</v>
+      </c>
+      <c r="J9" s="3">
         <v>300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>2800</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
@@ -902,38 +915,44 @@
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="F10" s="3">
         <v>-300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>-300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>-2500</v>
       </c>
-      <c r="G10" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="J10" s="3">
         <v>-300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>-200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>-2700</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -973,8 +992,14 @@
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1000,8 +1025,10 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1009,59 +1036,59 @@
         <v>2300</v>
       </c>
       <c r="E12" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="F12" s="3">
+        <v>2300</v>
+      </c>
+      <c r="G12" s="3">
         <v>4200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>2700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="J12" s="3">
+        <v>2100</v>
+      </c>
+      <c r="K12" s="3">
+        <v>3700</v>
+      </c>
+      <c r="L12" s="3">
         <v>2800</v>
       </c>
-      <c r="H12" s="3">
-        <v>2100</v>
-      </c>
-      <c r="I12" s="3">
-        <v>3700</v>
-      </c>
-      <c r="J12" s="3">
-        <v>2800</v>
-      </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>2300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>2000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>2600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>1600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>1500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>2500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>1800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>1400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>400</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1071,8 +1098,14 @@
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1142,8 +1175,14 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1168,11 +1207,11 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1213,8 +1252,14 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1239,11 +1284,11 @@
       <c r="J15" s="3">
         <v>0</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>3</v>
+      <c r="K15" s="3">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3">
+        <v>0</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>3</v>
@@ -1251,11 +1296,11 @@
       <c r="N15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
-      <c r="P15" s="3">
-        <v>0</v>
+      <c r="O15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
@@ -1284,8 +1329,14 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1308,68 +1359,70 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E17" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F17" s="3">
         <v>4500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>8200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>4400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>4400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>4900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>7700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>5300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>4600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>4800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>5300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>3300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>3300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>4700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>3600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>2500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>500</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1379,68 +1432,74 @@
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="F18" s="3">
         <v>-4500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-8200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-4400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-4400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-4900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-7700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-5200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-4600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-4800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-5200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-3300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-3300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-3500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-2500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-500</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1450,8 +1509,14 @@
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1477,8 +1542,10 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1489,38 +1556,38 @@
         <v>0</v>
       </c>
       <c r="F20" s="3">
+        <v>100</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
@@ -1531,14 +1598,14 @@
         <v>0</v>
       </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>-100</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1548,68 +1615,74 @@
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="F21" s="3">
         <v>-4600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-8200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-4100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-4800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-4800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-7800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-5300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-4600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-4500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-5100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-3300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-3200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-3600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-2400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-600</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1619,8 +1692,14 @@
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1645,11 +1724,11 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1690,68 +1769,74 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="F23" s="3">
         <v>-4500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-8100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-4000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-4700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-4700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-7700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-5100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-4600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-4600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-5100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-3300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-3200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-3600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-2400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-600</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1761,16 +1846,22 @@
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E24" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F24" s="3">
         <v>0</v>
@@ -1788,14 +1879,14 @@
         <v>0</v>
       </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>100</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
         <v>0</v>
       </c>
@@ -1817,11 +1908,11 @@
       <c r="T24" s="3">
         <v>0</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V24" s="3" t="s">
-        <v>3</v>
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
+        <v>0</v>
       </c>
       <c r="W24" s="3" t="s">
         <v>3</v>
@@ -1832,8 +1923,14 @@
       <c r="Y24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1903,8 +2000,14 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1912,59 +2015,59 @@
         <v>-4500</v>
       </c>
       <c r="E26" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="F26" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="G26" s="3">
         <v>-8100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-4000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-4700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-4700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-7700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-5100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-4700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-4600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-5100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-3300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-3200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-3600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-2500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-600</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1974,8 +2077,14 @@
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1983,59 +2092,59 @@
         <v>-4500</v>
       </c>
       <c r="E27" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="F27" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="G27" s="3">
         <v>-8100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-4000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-4700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-4700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-7700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-5100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-4700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-4600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-5100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-3300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-3200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-3600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-2500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-600</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2045,8 +2154,14 @@
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2116,8 +2231,14 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2187,8 +2308,14 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2258,8 +2385,14 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2329,8 +2462,14 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2341,38 +2480,38 @@
         <v>0</v>
       </c>
       <c r="F32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
@@ -2383,14 +2522,14 @@
         <v>0</v>
       </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>100</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2400,8 +2539,14 @@
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2409,59 +2554,59 @@
         <v>-4500</v>
       </c>
       <c r="E33" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="F33" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="G33" s="3">
         <v>-8100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-4000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-4700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-4700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-7700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-5100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-4700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-4600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-5100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-3300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-3200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-3600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-2500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-600</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2471,8 +2616,14 @@
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2542,8 +2693,14 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2551,59 +2708,59 @@
         <v>-4500</v>
       </c>
       <c r="E35" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="F35" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="G35" s="3">
         <v>-8100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-4000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-4700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-4700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-7700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-5100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-4700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-4600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-5100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-3300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-3200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-3600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-2500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-600</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2613,73 +2770,79 @@
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2689,8 +2852,14 @@
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2716,8 +2885,10 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2743,62 +2914,64 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>10400</v>
+      </c>
+      <c r="F41" s="3">
         <v>12000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>16900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>10600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>11800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>4300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>6300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>6000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>7300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>10900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>14300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>34300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>36900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>43200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>46600</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2814,8 +2987,14 @@
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2826,44 +3005,44 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>2000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>5000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>8000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>9900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>11800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>12800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>11900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>9900</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P42" s="3">
+      <c r="P42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R42" s="3">
         <v>40100</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2876,40 +3055,46 @@
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W42" s="3">
-        <v>0</v>
-      </c>
-      <c r="X42" s="3">
-        <v>0</v>
+      <c r="W42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>200</v>
+      </c>
+      <c r="E43" s="3">
+        <v>800</v>
+      </c>
+      <c r="F43" s="3">
         <v>400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>200</v>
-      </c>
-      <c r="G43" s="3">
-        <v>200</v>
-      </c>
-      <c r="H43" s="3">
-        <v>100</v>
       </c>
       <c r="I43" s="3">
         <v>200</v>
       </c>
       <c r="J43" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K43" s="3">
         <v>200</v>
@@ -2927,19 +3112,19 @@
         <v>200</v>
       </c>
       <c r="P43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Q43" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="R43" s="3">
         <v>100</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
+      <c r="S43" s="3">
+        <v>500</v>
+      </c>
+      <c r="T43" s="3">
+        <v>100</v>
       </c>
       <c r="U43" s="3" t="s">
         <v>3</v>
@@ -2956,8 +3141,14 @@
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2982,11 +3173,11 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3027,8 +3218,14 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3053,36 +3250,36 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>1500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>1400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>1800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>700</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3098,62 +3295,68 @@
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E46" s="3">
+        <v>11600</v>
+      </c>
+      <c r="F46" s="3">
         <v>13700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>18500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>13900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>17800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>13200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>17300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>19300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>21100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>24300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>25800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>36400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>37700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>41600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>44300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>47400</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3169,8 +3372,14 @@
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3192,24 +3401,24 @@
       <c r="I47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J47" s="3">
+      <c r="J47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3">
         <v>1000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>1900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>2900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>4900</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3222,11 +3431,11 @@
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T47" s="3">
-        <v>0</v>
-      </c>
-      <c r="U47" s="3">
-        <v>0</v>
+      <c r="T47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V47" s="3">
         <v>0</v>
@@ -3240,62 +3449,68 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>300</v>
+      </c>
+      <c r="E48" s="3">
+        <v>300</v>
+      </c>
+      <c r="F48" s="3">
         <v>400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>1000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>1000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>1100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>1200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>1200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>600</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3311,16 +3526,22 @@
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E49" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F49" s="3">
         <v>200</v>
@@ -3337,14 +3558,14 @@
       <c r="J49" s="3">
         <v>200</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
+      <c r="K49" s="3">
+        <v>200</v>
       </c>
       <c r="L49" s="3">
-        <v>0</v>
-      </c>
-      <c r="M49" s="3">
-        <v>0</v>
+        <v>200</v>
+      </c>
+      <c r="M49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N49" s="3">
         <v>0</v>
@@ -3382,8 +3603,14 @@
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3453,8 +3680,14 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3524,8 +3757,14 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3533,20 +3772,20 @@
         <v>100</v>
       </c>
       <c r="E52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G52" s="3">
+        <v>0</v>
+      </c>
+      <c r="H52" s="3">
+        <v>0</v>
+      </c>
+      <c r="I52" s="3">
         <v>100</v>
       </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
       <c r="J52" s="3">
         <v>0</v>
       </c>
@@ -3563,10 +3802,10 @@
         <v>0</v>
       </c>
       <c r="O52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q52" s="3">
         <v>100</v>
@@ -3574,11 +3813,11 @@
       <c r="R52" s="3">
         <v>100</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
+      <c r="S52" s="3">
+        <v>100</v>
+      </c>
+      <c r="T52" s="3">
+        <v>100</v>
       </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
@@ -3595,8 +3834,14 @@
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3666,62 +3911,68 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>12100</v>
+      </c>
+      <c r="F54" s="3">
         <v>14400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>19200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>14600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>18600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>14100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>18300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>21300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>24100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>28300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>31900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>37600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>39000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>42600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>45400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>48000</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3737,8 +3988,14 @@
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3764,8 +4021,10 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3791,62 +4050,64 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E57" s="3">
+        <v>900</v>
+      </c>
+      <c r="F57" s="3">
         <v>1100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>2000</v>
-      </c>
-      <c r="F57" s="3">
-        <v>1400</v>
-      </c>
-      <c r="G57" s="3">
-        <v>1300</v>
       </c>
       <c r="H57" s="3">
         <v>1400</v>
       </c>
       <c r="I57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="K57" s="3">
         <v>900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>2200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>1600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>1000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>2100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>1000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>900</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3862,8 +4123,14 @@
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3889,10 +4156,10 @@
         <v>300</v>
       </c>
       <c r="K58" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="L58" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="M58" s="3">
         <v>100</v>
@@ -3910,13 +4177,13 @@
         <v>100</v>
       </c>
       <c r="R58" s="3">
-        <v>0</v>
-      </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="S58" s="3">
+        <v>100</v>
+      </c>
+      <c r="T58" s="3">
+        <v>0</v>
       </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
@@ -3933,62 +4200,68 @@
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E59" s="3">
+        <v>300</v>
+      </c>
+      <c r="F59" s="3">
         <v>700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>1000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>1200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>1400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>1300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>100</v>
-      </c>
-      <c r="K59" s="3">
-        <v>2400</v>
-      </c>
-      <c r="L59" s="3">
-        <v>3200</v>
       </c>
       <c r="M59" s="3">
         <v>2400</v>
       </c>
       <c r="N59" s="3">
+        <v>3200</v>
+      </c>
+      <c r="O59" s="3">
+        <v>2400</v>
+      </c>
+      <c r="P59" s="3">
         <v>2000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>1900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>2700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>1400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>1400</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4004,62 +4277,68 @@
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>3900</v>
+      </c>
+      <c r="F60" s="3">
         <v>4600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>6500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>5000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>4900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>5800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>5600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>5200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>4100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>4300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>3400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>4200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>2600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>3600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>2500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>2300</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4075,46 +4354,52 @@
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>300</v>
+      </c>
+      <c r="E61" s="3">
+        <v>400</v>
+      </c>
+      <c r="F61" s="3">
         <v>500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>900</v>
-      </c>
-      <c r="K61" s="3">
-        <v>500</v>
-      </c>
-      <c r="L61" s="3">
-        <v>500</v>
       </c>
       <c r="M61" s="3">
         <v>500</v>
       </c>
       <c r="N61" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="O61" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="P61" s="3">
         <v>600</v>
@@ -4123,14 +4408,14 @@
         <v>600</v>
       </c>
       <c r="R61" s="3">
+        <v>600</v>
+      </c>
+      <c r="S61" s="3">
+        <v>600</v>
+      </c>
+      <c r="T61" s="3">
         <v>700</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -4146,8 +4431,14 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4172,36 +4463,36 @@
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3">
         <v>600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>1000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>1000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>600</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4217,8 +4508,14 @@
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4288,8 +4585,14 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4359,8 +4662,14 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4430,62 +4739,68 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>4800</v>
+      </c>
+      <c r="F66" s="3">
         <v>5500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>7400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>5900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>6000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>6800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>7200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>6200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>5200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>5700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>4900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>5800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>4200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>5000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>4000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>3600</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4501,8 +4816,14 @@
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4528,8 +4849,10 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4599,8 +4922,14 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4670,8 +4999,14 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4741,8 +5076,14 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4812,62 +5153,68 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-85700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-81200</v>
+      </c>
+      <c r="F72" s="3">
         <v>-77400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-72900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-64800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-60800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-56100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-51300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-43700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-38500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-33800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-29300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-24200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-20900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-17700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-13000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-9500</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4883,8 +5230,14 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4954,8 +5307,14 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5025,8 +5384,14 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5096,62 +5461,68 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E76" s="3">
+        <v>7300</v>
+      </c>
+      <c r="F76" s="3">
         <v>8900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>11800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>8600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>12600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>7300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>11100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>15100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>18900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>22700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>27000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>31800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>34800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>37500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>41400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>44500</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5167,8 +5538,14 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5238,73 +5615,79 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5314,8 +5697,14 @@
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -5323,59 +5712,59 @@
         <v>-4500</v>
       </c>
       <c r="E81" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="F81" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="G81" s="3">
         <v>-8100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-4000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-4700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-4700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-7700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-5100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-4700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-4600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-5100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-3300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-3200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-3600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-2500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-600</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5385,8 +5774,14 @@
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5412,8 +5807,10 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5468,11 +5865,11 @@
       <c r="T83" s="3">
         <v>0</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V83" s="3" t="s">
-        <v>3</v>
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+      <c r="V83" s="3">
+        <v>0</v>
       </c>
       <c r="W83" s="3" t="s">
         <v>3</v>
@@ -5483,8 +5880,14 @@
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5554,8 +5957,14 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5625,8 +6034,14 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5696,8 +6111,14 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5767,8 +6188,14 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5838,68 +6265,74 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="F89" s="3">
         <v>-6100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-5800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-3600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-5700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-4000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-5000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-4200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-3900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-3300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-5100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-2400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-4100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-3200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-2800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-800</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5909,8 +6342,14 @@
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5936,25 +6375,27 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>3</v>
+      <c r="F91" s="3">
+        <v>0</v>
       </c>
       <c r="G91" s="3">
         <v>0</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I91" s="3">
         <v>0</v>
@@ -5963,14 +6404,14 @@
         <v>0</v>
       </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
@@ -5992,11 +6433,11 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
+        <v>0</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>3</v>
@@ -6007,8 +6448,14 @@
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6078,8 +6525,14 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6149,47 +6602,53 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
         <v>2000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>3000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>3100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>1900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>3000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>2100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>100</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-14900</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
         <v>0</v>
       </c>
@@ -6205,11 +6664,11 @@
       <c r="T94" s="3">
         <v>0</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
+        <v>0</v>
       </c>
       <c r="W94" s="3" t="s">
         <v>3</v>
@@ -6220,8 +6679,14 @@
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6247,8 +6712,10 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6273,11 +6740,11 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -6318,8 +6785,14 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6389,8 +6862,14 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6460,8 +6939,14 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6531,38 +7016,44 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E100" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F100" s="3">
         <v>800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>10000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>9600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>2200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>700</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
         <v>0</v>
       </c>
@@ -6576,23 +7067,23 @@
         <v>0</v>
       </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>-200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>42000</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>1400</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6602,53 +7093,59 @@
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E101" s="3">
+        <v>500</v>
+      </c>
+      <c r="F101" s="3">
         <v>-100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>100</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-100</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
         <v>200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-100</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
         <v>100</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
       <c r="R101" s="3">
         <v>0</v>
       </c>
@@ -6658,11 +7155,11 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V101" s="3" t="s">
-        <v>3</v>
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
+        <v>0</v>
       </c>
       <c r="W101" s="3" t="s">
         <v>3</v>
@@ -6673,68 +7170,74 @@
       <c r="Y101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F102" s="3">
         <v>-4900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>6300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-1200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>7500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-2000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-1300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-3600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-3400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-20000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-2500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-4100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-3400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>39100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>600</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6742,6 +7245,12 @@
         <v>3</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GANX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GANX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="92">
   <si>
     <t>GANX</t>
   </si>
@@ -656,105 +656,106 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
@@ -767,8 +768,11 @@
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -787,30 +791,30 @@
       <c r="H8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3">
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L8" s="3">
+      <c r="L8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M8" s="3">
         <v>100</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
-      </c>
       <c r="N8" s="3">
         <v>0</v>
       </c>
       <c r="O8" s="3">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3">
         <v>100</v>
       </c>
-      <c r="P8" s="3">
-        <v>0</v>
-      </c>
       <c r="Q8" s="3">
         <v>0</v>
       </c>
@@ -818,19 +822,19 @@
         <v>0</v>
       </c>
       <c r="S8" s="3">
+        <v>0</v>
+      </c>
+      <c r="T8" s="3">
         <v>100</v>
       </c>
-      <c r="T8" s="3">
-        <v>0</v>
-      </c>
       <c r="U8" s="3">
         <v>0</v>
       </c>
       <c r="V8" s="3">
         <v>0</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>3</v>
+      <c r="W8" s="3">
+        <v>0</v>
       </c>
       <c r="X8" s="3" t="s">
         <v>3</v>
@@ -838,14 +842,17 @@
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z8" s="3">
-        <v>0</v>
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -853,32 +860,32 @@
         <v>3</v>
       </c>
       <c r="E9" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F9" s="3">
         <v>9900</v>
-      </c>
-      <c r="F9" s="3">
-        <v>300</v>
       </c>
       <c r="G9" s="3">
         <v>300</v>
       </c>
       <c r="H9" s="3">
+        <v>300</v>
+      </c>
+      <c r="I9" s="3">
         <v>2500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>10700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2800</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
@@ -921,8 +928,11 @@
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -930,32 +940,32 @@
         <v>3</v>
       </c>
       <c r="E10" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="F10" s="3">
         <v>-9900</v>
-      </c>
-      <c r="F10" s="3">
-        <v>-300</v>
       </c>
       <c r="G10" s="3">
         <v>-300</v>
       </c>
       <c r="H10" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I10" s="3">
         <v>-2500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-10700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-2700</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
@@ -998,8 +1008,11 @@
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1027,70 +1040,71 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E12" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F12" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="G12" s="3">
         <v>2300</v>
       </c>
-      <c r="E12" s="3">
-        <v>-8700</v>
-      </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
+        <v>4200</v>
+      </c>
+      <c r="I12" s="3">
+        <v>2700</v>
+      </c>
+      <c r="J12" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="K12" s="3">
+        <v>2100</v>
+      </c>
+      <c r="L12" s="3">
+        <v>3700</v>
+      </c>
+      <c r="M12" s="3">
+        <v>2800</v>
+      </c>
+      <c r="N12" s="3">
         <v>2300</v>
       </c>
-      <c r="G12" s="3">
-        <v>4200</v>
-      </c>
-      <c r="H12" s="3">
-        <v>2700</v>
-      </c>
-      <c r="I12" s="3">
-        <v>-8400</v>
-      </c>
-      <c r="J12" s="3">
-        <v>2100</v>
-      </c>
-      <c r="K12" s="3">
-        <v>3700</v>
-      </c>
-      <c r="L12" s="3">
-        <v>2800</v>
-      </c>
-      <c r="M12" s="3">
-        <v>2300</v>
-      </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>2000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>2600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>2500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1400</v>
-      </c>
-      <c r="U12" s="3">
-        <v>400</v>
       </c>
       <c r="V12" s="3">
         <v>400</v>
       </c>
-      <c r="W12" s="3" t="s">
-        <v>3</v>
+      <c r="W12" s="3">
+        <v>400</v>
       </c>
       <c r="X12" s="3" t="s">
         <v>3</v>
@@ -1104,8 +1118,11 @@
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1181,8 +1198,11 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1213,8 +1233,8 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1258,8 +1278,11 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1290,8 +1313,8 @@
       <c r="L15" s="3">
         <v>0</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>3</v>
+      <c r="M15" s="3">
+        <v>0</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>3</v>
@@ -1302,8 +1325,8 @@
       <c r="P15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
+      <c r="Q15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
@@ -1335,8 +1358,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1361,70 +1387,71 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E17" s="3">
         <v>4400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>8200</v>
-      </c>
-      <c r="H17" s="3">
-        <v>4400</v>
       </c>
       <c r="I17" s="3">
         <v>4400</v>
       </c>
       <c r="J17" s="3">
+        <v>4400</v>
+      </c>
+      <c r="K17" s="3">
         <v>4900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5300</v>
-      </c>
-      <c r="P17" s="3">
-        <v>3300</v>
       </c>
       <c r="Q17" s="3">
         <v>3300</v>
       </c>
       <c r="R17" s="3">
+        <v>3300</v>
+      </c>
+      <c r="S17" s="3">
         <v>4700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2500</v>
-      </c>
-      <c r="U17" s="3">
-        <v>500</v>
       </c>
       <c r="V17" s="3">
         <v>500</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
+      <c r="W17" s="3">
+        <v>500</v>
       </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
@@ -1438,70 +1465,73 @@
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-4400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-3300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-4500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-8200</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-4400</v>
       </c>
       <c r="I18" s="3">
         <v>-4400</v>
       </c>
       <c r="J18" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="K18" s="3">
         <v>-4900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-7700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-5200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-4600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-4800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-5200</v>
-      </c>
-      <c r="P18" s="3">
-        <v>-3300</v>
       </c>
       <c r="Q18" s="3">
         <v>-3300</v>
       </c>
       <c r="R18" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="S18" s="3">
         <v>-4700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-3500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-2500</v>
-      </c>
-      <c r="U18" s="3">
-        <v>-500</v>
       </c>
       <c r="V18" s="3">
         <v>-500</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
+      <c r="W18" s="3">
+        <v>-500</v>
       </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
@@ -1515,8 +1545,11 @@
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1544,52 +1577,53 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>600</v>
+      </c>
+      <c r="E20" s="3">
         <v>100</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>100</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>-300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>200</v>
-      </c>
-      <c r="O20" s="3">
-        <v>100</v>
       </c>
       <c r="P20" s="3">
         <v>100</v>
       </c>
       <c r="Q20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R20" s="3">
         <v>0</v>
@@ -1604,11 +1638,11 @@
         <v>0</v>
       </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>-100</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1621,71 +1655,74 @@
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-4400</v>
+        <v>-5700</v>
       </c>
       <c r="E21" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="F21" s="3">
         <v>-3300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-4600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-8200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-4100</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-4800</v>
       </c>
       <c r="J21" s="3">
         <v>-4800</v>
       </c>
       <c r="K21" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="L21" s="3">
         <v>-7800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-5300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-4600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-4500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-5100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-3200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-4700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-3600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-2400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-600</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1698,8 +1735,11 @@
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1730,8 +1770,8 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1775,71 +1815,74 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-4400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-3300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-4500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-8100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-4000</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-4700</v>
       </c>
       <c r="J23" s="3">
         <v>-4700</v>
       </c>
       <c r="K23" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="L23" s="3">
         <v>-7700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-5100</v>
-      </c>
-      <c r="M23" s="3">
-        <v>-4600</v>
       </c>
       <c r="N23" s="3">
         <v>-4600</v>
       </c>
       <c r="O23" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="P23" s="3">
         <v>-5100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-3200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-4700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-3600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-600</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1852,8 +1895,11 @@
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1861,11 +1907,11 @@
         <v>100</v>
       </c>
       <c r="E24" s="3">
+        <v>100</v>
+      </c>
+      <c r="F24" s="3">
         <v>500</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
         <v>0</v>
       </c>
@@ -1885,11 +1931,11 @@
         <v>0</v>
       </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>100</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
         <v>0</v>
       </c>
@@ -1914,8 +1960,8 @@
       <c r="V24" s="3">
         <v>0</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>3</v>
+      <c r="W24" s="3">
+        <v>0</v>
       </c>
       <c r="X24" s="3" t="s">
         <v>3</v>
@@ -1929,8 +1975,11 @@
       <c r="AA24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2006,71 +2055,74 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-4500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-3800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-4500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-8100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-4000</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-4700</v>
       </c>
       <c r="J26" s="3">
         <v>-4700</v>
       </c>
       <c r="K26" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="L26" s="3">
         <v>-7700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-5100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-4700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-4600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-5100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-3200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-4700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-3600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-2500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-600</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2083,71 +2135,74 @@
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-4500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-3800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-4500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-8100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-4000</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-4700</v>
       </c>
       <c r="J27" s="3">
         <v>-4700</v>
       </c>
       <c r="K27" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="L27" s="3">
         <v>-7700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-5100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-4700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-4600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-5100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-3200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-4700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-3600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-2500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-600</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2160,8 +2215,11 @@
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2237,8 +2295,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2314,8 +2375,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2391,8 +2455,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2468,52 +2535,55 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-100</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>-100</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-200</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-100</v>
       </c>
       <c r="P32" s="3">
         <v>-100</v>
       </c>
       <c r="Q32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="R32" s="3">
         <v>0</v>
@@ -2528,11 +2598,11 @@
         <v>0</v>
       </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>100</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2545,71 +2615,74 @@
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-4500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-3800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-4500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-8100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-4000</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-4700</v>
       </c>
       <c r="J33" s="3">
         <v>-4700</v>
       </c>
       <c r="K33" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="L33" s="3">
         <v>-7700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-5100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-4700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-4600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-5100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-3200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-4700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-3600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-2500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-600</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2622,8 +2695,11 @@
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2699,71 +2775,74 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-4500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-3800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-4500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-8100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-4000</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-4700</v>
       </c>
       <c r="J35" s="3">
         <v>-4700</v>
       </c>
       <c r="K35" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="L35" s="3">
         <v>-7700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-5100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-4700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-4600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-5100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-3200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-4700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-3600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-2500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-600</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2776,76 +2855,79 @@
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2858,8 +2940,11 @@
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2887,8 +2972,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2916,65 +3002,66 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E41" s="3">
         <v>9100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>10400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>12000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>16900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>10600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>11800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>10900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>14300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>34300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>36900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>43200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>46600</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2993,8 +3080,11 @@
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3011,41 +3101,41 @@
         <v>0</v>
       </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>2000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>5000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>8000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>9900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>11800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>12800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>11900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>9900</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R42" s="3">
+      <c r="R42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S42" s="3">
         <v>40100</v>
       </c>
-      <c r="S42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3061,8 +3151,8 @@
       <c r="X42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y42" s="3">
-        <v>0</v>
+      <c r="Y42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z42" s="3">
         <v>0</v>
@@ -3070,34 +3160,37 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E43" s="3">
+        <v>900</v>
+      </c>
+      <c r="F43" s="3">
         <v>800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>300</v>
-      </c>
-      <c r="H43" s="3">
-        <v>200</v>
       </c>
       <c r="I43" s="3">
         <v>200</v>
       </c>
       <c r="J43" s="3">
+        <v>200</v>
+      </c>
+      <c r="K43" s="3">
         <v>100</v>
-      </c>
-      <c r="K43" s="3">
-        <v>200</v>
       </c>
       <c r="L43" s="3">
         <v>200</v>
@@ -3118,17 +3211,17 @@
         <v>200</v>
       </c>
       <c r="R43" s="3">
+        <v>200</v>
+      </c>
+      <c r="S43" s="3">
         <v>100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>100</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3147,8 +3240,11 @@
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3179,8 +3275,8 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -3224,8 +3320,11 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3256,32 +3355,32 @@
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3">
         <v>800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>500</v>
-      </c>
-      <c r="S45" s="3">
-        <v>700</v>
       </c>
       <c r="T45" s="3">
         <v>700</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
+      <c r="U45" s="3">
+        <v>700</v>
       </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
@@ -3301,65 +3400,68 @@
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E46" s="3">
         <v>11200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>11600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>13700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>18500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>13900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>17800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>13200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>17300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>19300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>21100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>24300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>25800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>36400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>37700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>41600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>44300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>47400</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3378,8 +3480,11 @@
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3407,21 +3512,21 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3">
         <v>1000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>4900</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3437,8 +3542,8 @@
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V47" s="3">
-        <v>0</v>
+      <c r="V47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W47" s="3">
         <v>0</v>
@@ -3455,8 +3560,11 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3467,53 +3575,53 @@
         <v>300</v>
       </c>
       <c r="F48" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="G48" s="3">
         <v>400</v>
       </c>
       <c r="H48" s="3">
+        <v>400</v>
+      </c>
+      <c r="I48" s="3">
         <v>500</v>
-      </c>
-      <c r="I48" s="3">
-        <v>600</v>
       </c>
       <c r="J48" s="3">
         <v>600</v>
       </c>
       <c r="K48" s="3">
+        <v>600</v>
+      </c>
+      <c r="L48" s="3">
         <v>700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>800</v>
-      </c>
-      <c r="M48" s="3">
-        <v>1000</v>
       </c>
       <c r="N48" s="3">
         <v>1000</v>
       </c>
       <c r="O48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="P48" s="3">
         <v>1100</v>
-      </c>
-      <c r="P48" s="3">
-        <v>1200</v>
       </c>
       <c r="Q48" s="3">
         <v>1200</v>
       </c>
       <c r="R48" s="3">
-        <v>900</v>
+        <v>1200</v>
       </c>
       <c r="S48" s="3">
         <v>900</v>
       </c>
       <c r="T48" s="3">
+        <v>900</v>
+      </c>
+      <c r="U48" s="3">
         <v>600</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3532,8 +3640,11 @@
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3544,7 +3655,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G49" s="3">
         <v>200</v>
@@ -3564,11 +3675,11 @@
       <c r="L49" s="3">
         <v>200</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N49" s="3">
-        <v>0</v>
+      <c r="M49" s="3">
+        <v>200</v>
+      </c>
+      <c r="N49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O49" s="3">
         <v>0</v>
@@ -3609,8 +3720,11 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3686,8 +3800,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3763,8 +3880,11 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3778,17 +3898,17 @@
         <v>100</v>
       </c>
       <c r="G52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H52" s="3">
         <v>0</v>
       </c>
       <c r="I52" s="3">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3">
         <v>100</v>
       </c>
-      <c r="J52" s="3">
-        <v>0</v>
-      </c>
       <c r="K52" s="3">
         <v>0</v>
       </c>
@@ -3808,7 +3928,7 @@
         <v>0</v>
       </c>
       <c r="Q52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R52" s="3">
         <v>100</v>
@@ -3819,8 +3939,8 @@
       <c r="T52" s="3">
         <v>100</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
+      <c r="U52" s="3">
+        <v>100</v>
       </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
@@ -3840,8 +3960,11 @@
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3917,65 +4040,68 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E54" s="3">
         <v>11600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>12100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>14400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>19200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>14600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>18600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>14100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>18300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>21300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>24100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>28300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>31900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>37600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>39000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>42600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>45400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>48000</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3994,8 +4120,11 @@
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4023,8 +4152,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4052,65 +4182,66 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E57" s="3">
         <v>2200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>900</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4129,8 +4260,11 @@
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4162,7 +4296,7 @@
         <v>300</v>
       </c>
       <c r="M58" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="N58" s="3">
         <v>100</v>
@@ -4183,10 +4317,10 @@
         <v>100</v>
       </c>
       <c r="T58" s="3">
-        <v>0</v>
-      </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="U58" s="3">
+        <v>0</v>
       </c>
       <c r="V58" s="3" t="s">
         <v>3</v>
@@ -4206,64 +4340,67 @@
       <c r="AA58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2600</v>
+        <v>2200</v>
       </c>
       <c r="E59" s="3">
+        <v>200</v>
+      </c>
+      <c r="F59" s="3">
         <v>300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2700</v>
-      </c>
-      <c r="S59" s="3">
-        <v>1400</v>
       </c>
       <c r="T59" s="3">
         <v>1400</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
+      <c r="U59" s="3">
+        <v>1400</v>
       </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
@@ -4283,65 +4420,68 @@
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E60" s="3">
         <v>5000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2300</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4360,40 +4500,43 @@
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>400</v>
+      </c>
+      <c r="E61" s="3">
         <v>300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>400</v>
-      </c>
-      <c r="F61" s="3">
-        <v>500</v>
       </c>
       <c r="G61" s="3">
         <v>500</v>
       </c>
       <c r="H61" s="3">
+        <v>500</v>
+      </c>
+      <c r="I61" s="3">
         <v>600</v>
-      </c>
-      <c r="I61" s="3">
-        <v>700</v>
       </c>
       <c r="J61" s="3">
         <v>700</v>
       </c>
       <c r="K61" s="3">
+        <v>700</v>
+      </c>
+      <c r="L61" s="3">
         <v>800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>900</v>
-      </c>
-      <c r="M61" s="3">
-        <v>500</v>
       </c>
       <c r="N61" s="3">
         <v>500</v>
@@ -4402,7 +4545,7 @@
         <v>500</v>
       </c>
       <c r="P61" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="Q61" s="3">
         <v>600</v>
@@ -4414,11 +4557,11 @@
         <v>600</v>
       </c>
       <c r="T61" s="3">
+        <v>600</v>
+      </c>
+      <c r="U61" s="3">
         <v>700</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -4437,8 +4580,11 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4469,33 +4615,33 @@
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3">
         <v>600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>900</v>
-      </c>
-      <c r="P62" s="3">
-        <v>1000</v>
       </c>
       <c r="Q62" s="3">
         <v>1000</v>
       </c>
       <c r="R62" s="3">
+        <v>1000</v>
+      </c>
+      <c r="S62" s="3">
         <v>800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>600</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4514,8 +4660,11 @@
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4591,8 +4740,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4668,8 +4820,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4745,65 +4900,68 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E66" s="3">
         <v>5800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3600</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4822,8 +4980,11 @@
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4851,8 +5012,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4928,8 +5090,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5005,8 +5170,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5082,8 +5250,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5159,65 +5330,68 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-91500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-85700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-81200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-77400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-72900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-64800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-60800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-56100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-51300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-43700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-38500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-33800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-29300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-24200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-20900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-17700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-13000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-9500</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5236,8 +5410,11 @@
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5313,8 +5490,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5390,8 +5570,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5467,65 +5650,68 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E76" s="3">
         <v>5800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>11800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>12600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>11100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>15100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>18900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>22700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>27000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>31800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>34800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>37500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>41400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>44500</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5544,8 +5730,11 @@
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5621,76 +5810,79 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5703,71 +5895,74 @@
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-4500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-3800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-4500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-8100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-4000</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-4700</v>
       </c>
       <c r="J81" s="3">
         <v>-4700</v>
       </c>
       <c r="K81" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="L81" s="3">
         <v>-7700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-5100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-4700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-4600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-5100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-3200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-4700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-3600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-2500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-600</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5780,8 +5975,11 @@
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5809,8 +6007,9 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5871,8 +6070,8 @@
       <c r="V83" s="3">
         <v>0</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>3</v>
+      <c r="W83" s="3">
+        <v>0</v>
       </c>
       <c r="X83" s="3" t="s">
         <v>3</v>
@@ -5886,8 +6085,11 @@
       <c r="AA83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5963,8 +6165,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6040,8 +6245,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6117,8 +6325,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6194,8 +6405,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6271,71 +6485,74 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-3800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-3500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-6100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-5800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-3600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-5700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-4000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-5000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-4200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-3900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-3300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-5100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-4100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-2200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-3200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-2800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-800</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6348,8 +6565,11 @@
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6377,16 +6597,17 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
@@ -6394,11 +6615,11 @@
       <c r="G91" s="3">
         <v>0</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
+      <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J91" s="3">
         <v>0</v>
@@ -6410,11 +6631,11 @@
         <v>0</v>
       </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
@@ -6439,8 +6660,8 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
+      <c r="W91" s="3">
+        <v>0</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
@@ -6454,8 +6675,11 @@
       <c r="AA91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6531,8 +6755,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6608,50 +6835,53 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
+      <c r="E94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F94" s="3">
         <v>0</v>
       </c>
       <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>2000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>3000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>3100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>1900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>3000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>2100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>100</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>-14900</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
         <v>0</v>
       </c>
@@ -6670,8 +6900,8 @@
       <c r="V94" s="3">
         <v>0</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
+      <c r="W94" s="3">
+        <v>0</v>
       </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
@@ -6685,8 +6915,11 @@
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6714,8 +6947,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6746,8 +6980,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -6791,8 +7025,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6868,8 +7105,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6945,8 +7185,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7022,41 +7265,44 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E100" s="3">
         <v>2400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>10000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>9600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>700</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
         <v>0</v>
       </c>
@@ -7073,20 +7319,20 @@
         <v>0</v>
       </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>-200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>42000</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>1400</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7099,56 +7345,59 @@
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
         <v>-400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>100</v>
       </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
       <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
         <v>200</v>
-      </c>
-      <c r="J101" s="3">
-        <v>-100</v>
       </c>
       <c r="K101" s="3">
         <v>-100</v>
       </c>
       <c r="L101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>200</v>
-      </c>
-      <c r="N101" s="3">
-        <v>-100</v>
       </c>
       <c r="O101" s="3">
         <v>-100</v>
       </c>
       <c r="P101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
         <v>100</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
       <c r="S101" s="3">
         <v>0</v>
       </c>
@@ -7161,8 +7410,8 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-      <c r="W101" s="3" t="s">
-        <v>3</v>
+      <c r="W101" s="3">
+        <v>0</v>
       </c>
       <c r="X101" s="3" t="s">
         <v>3</v>
@@ -7176,71 +7425,74 @@
       <c r="AA101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-4900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>6300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>7500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-3600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-3400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-20000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-4100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-2200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-3400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>39100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>600</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7251,6 +7503,9 @@
         <v>3</v>
       </c>
       <c r="AA102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GANX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GANX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="92">
   <si>
     <t>GANX</t>
   </si>
@@ -656,116 +656,117 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
@@ -775,8 +776,14 @@
       <c r="AC7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -801,107 +808,113 @@
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
+      <c r="K8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N8" s="3">
+      <c r="M8" s="3">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8" s="3">
         <v>100</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
-      </c>
-      <c r="P8" s="3">
-        <v>0</v>
-      </c>
       <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+      <c r="S8" s="3">
         <v>100</v>
       </c>
-      <c r="R8" s="3">
-        <v>0</v>
-      </c>
-      <c r="S8" s="3">
-        <v>0</v>
-      </c>
       <c r="T8" s="3">
         <v>0</v>
       </c>
       <c r="U8" s="3">
+        <v>0</v>
+      </c>
+      <c r="V8" s="3">
+        <v>0</v>
+      </c>
+      <c r="W8" s="3">
         <v>100</v>
       </c>
-      <c r="V8" s="3">
-        <v>0</v>
-      </c>
-      <c r="W8" s="3">
-        <v>0</v>
-      </c>
       <c r="X8" s="3">
         <v>0</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z8" s="3" t="s">
-        <v>3</v>
+      <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="3">
+        <v>0</v>
       </c>
       <c r="AA8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB8" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F9" s="3">
         <v>2800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>2700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>2200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>1200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>2600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>4400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>2500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>10700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>2800</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
@@ -941,50 +954,56 @@
       <c r="AC9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="F10" s="3">
         <v>-2800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>-2700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>-2200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>-1200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>-2600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>-4400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>-2500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>-10700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>-300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>-200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>-2700</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1024,8 +1043,14 @@
       <c r="AC10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1055,80 +1080,82 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E12" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F12" s="3">
         <v>3600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>3300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>2400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
+        <v>2700</v>
+      </c>
+      <c r="J12" s="3">
+        <v>2900</v>
+      </c>
+      <c r="K12" s="3">
+        <v>4600</v>
+      </c>
+      <c r="L12" s="3">
+        <v>2700</v>
+      </c>
+      <c r="M12" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="N12" s="3">
+        <v>2100</v>
+      </c>
+      <c r="O12" s="3">
+        <v>3700</v>
+      </c>
+      <c r="P12" s="3">
+        <v>2800</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>2300</v>
+      </c>
+      <c r="R12" s="3">
+        <v>2000</v>
+      </c>
+      <c r="S12" s="3">
         <v>2600</v>
       </c>
-      <c r="H12" s="3">
-        <v>2900</v>
-      </c>
-      <c r="I12" s="3">
-        <v>4600</v>
-      </c>
-      <c r="J12" s="3">
-        <v>2700</v>
-      </c>
-      <c r="K12" s="3">
-        <v>-8400</v>
-      </c>
-      <c r="L12" s="3">
-        <v>2100</v>
-      </c>
-      <c r="M12" s="3">
-        <v>3700</v>
-      </c>
-      <c r="N12" s="3">
-        <v>2800</v>
-      </c>
-      <c r="O12" s="3">
-        <v>2300</v>
-      </c>
-      <c r="P12" s="3">
-        <v>2000</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>2600</v>
-      </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>1600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>1500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>2500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>1800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>1400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>400</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>400</v>
       </c>
-      <c r="Y12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1138,8 +1165,14 @@
       <c r="AC12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1221,8 +1254,14 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1259,11 +1298,11 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1304,8 +1343,14 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1342,11 +1387,11 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P15" s="3" t="s">
-        <v>3</v>
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3">
+        <v>0</v>
       </c>
       <c r="Q15" s="3" t="s">
         <v>3</v>
@@ -1354,11 +1399,11 @@
       <c r="R15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S15" s="3">
-        <v>0</v>
-      </c>
-      <c r="T15" s="3">
-        <v>0</v>
+      <c r="S15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U15" s="3">
         <v>0</v>
@@ -1387,8 +1432,14 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1415,80 +1466,82 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E17" s="3">
+        <v>4500</v>
+      </c>
+      <c r="F17" s="3">
         <v>4800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>5100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>4400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>3300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>4500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>8200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>4400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>4400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>4900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>7700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>5300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>4600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>4800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>5300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>3300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>3300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>4700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>3600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>2500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>500</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1498,80 +1551,86 @@
       <c r="AC17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="F18" s="3">
         <v>-4800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-5100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-4400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-3300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-4500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-8200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-4400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-4400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-4900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-7700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-5200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-4600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-5200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-3300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-3300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-4700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-3500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-2500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-500</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1581,8 +1640,14 @@
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1612,22 +1677,24 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E20" s="3">
+        <v>100</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>600</v>
-      </c>
-      <c r="F20" s="3">
-        <v>100</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
       </c>
       <c r="H20" s="3">
         <v>100</v>
@@ -1636,38 +1703,38 @@
         <v>0</v>
       </c>
       <c r="J20" s="3">
+        <v>100</v>
+      </c>
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
         <v>0</v>
       </c>
@@ -1678,14 +1745,14 @@
         <v>0</v>
       </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-100</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1695,80 +1762,86 @@
       <c r="AC20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="F21" s="3">
         <v>-4800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-5700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-4500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-3300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-4600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-8200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-4100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-4800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-4800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-7800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-5300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-4600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-5100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-3300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-3200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-4700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-3600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-2400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-600</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1778,8 +1851,14 @@
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1816,11 +1895,11 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1861,80 +1940,86 @@
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="F23" s="3">
         <v>-4700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-5700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-4400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-3300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-4500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-8100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-4000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-4700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-4700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-7700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-5100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-4600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-5100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-3300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-3200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-4700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-3600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-2400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-600</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1944,29 +2029,35 @@
       <c r="AC23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="E24" s="3">
         <v>100</v>
       </c>
       <c r="F24" s="3">
+        <v>500</v>
+      </c>
+      <c r="G24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
+        <v>100</v>
+      </c>
+      <c r="I24" s="3">
         <v>500</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
         <v>0</v>
       </c>
@@ -1983,14 +2074,14 @@
         <v>0</v>
       </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>100</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
         <v>0</v>
       </c>
@@ -2012,11 +2103,11 @@
       <c r="X24" s="3">
         <v>0</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z24" s="3" t="s">
-        <v>3</v>
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>0</v>
       </c>
       <c r="AA24" s="3" t="s">
         <v>3</v>
@@ -2027,8 +2118,14 @@
       <c r="AC24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2110,80 +2207,86 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="F26" s="3">
         <v>-5300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-5800</v>
-      </c>
-      <c r="F26" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-3800</v>
       </c>
       <c r="H26" s="3">
         <v>-4500</v>
       </c>
       <c r="I26" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="J26" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="K26" s="3">
         <v>-8100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-4000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-4700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-4700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-7700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-5100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-4700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-5100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-3300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-3200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-4700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-3600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-2500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-600</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2193,80 +2296,86 @@
       <c r="AC26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="F27" s="3">
         <v>-5300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-5800</v>
-      </c>
-      <c r="F27" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-3800</v>
       </c>
       <c r="H27" s="3">
         <v>-4500</v>
       </c>
       <c r="I27" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="J27" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="K27" s="3">
         <v>-8100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-4000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-4700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-4700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-7700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-5100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-4700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-5100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-3300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-3200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-4700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-3600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-2500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-600</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2276,8 +2385,14 @@
       <c r="AC27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2359,8 +2474,14 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2442,8 +2563,14 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2525,8 +2652,14 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2608,22 +2741,28 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>-600</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
       </c>
       <c r="H32" s="3">
         <v>-100</v>
@@ -2632,38 +2771,38 @@
         <v>0</v>
       </c>
       <c r="J32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
         <v>0</v>
       </c>
@@ -2674,14 +2813,14 @@
         <v>0</v>
       </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>100</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2691,80 +2830,86 @@
       <c r="AC32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="F33" s="3">
         <v>-5300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-5800</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-3800</v>
       </c>
       <c r="H33" s="3">
         <v>-4500</v>
       </c>
       <c r="I33" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="J33" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="K33" s="3">
         <v>-8100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-4000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-4700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-4700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-7700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-5100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-4700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-5100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-3300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-3200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-4700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-3600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-2500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-600</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2774,8 +2919,14 @@
       <c r="AC33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2857,80 +3008,86 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="F35" s="3">
         <v>-5300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-5800</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-3800</v>
       </c>
       <c r="H35" s="3">
         <v>-4500</v>
       </c>
       <c r="I35" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="J35" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="K35" s="3">
         <v>-8100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-4000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-4700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-4700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-7700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-5100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-4700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-5100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-3300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-3200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-4700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-3600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-2500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-600</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2940,85 +3097,91 @@
       <c r="AC35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
@@ -3028,8 +3191,14 @@
       <c r="AC38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3059,8 +3228,10 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3090,74 +3261,76 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>16500</v>
+      </c>
+      <c r="E41" s="3">
+        <v>20800</v>
+      </c>
+      <c r="F41" s="3">
         <v>8800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>6700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>9100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>10400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>12000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>16900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>10600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>11800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>4300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>6300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>6000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>7300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>10900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>14300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>34300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>36900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>43200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>46600</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3173,8 +3346,14 @@
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3197,44 +3376,44 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>2000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>5000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>8000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>9900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>11800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>12800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>11900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>9900</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T42" s="3">
+      <c r="T42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V42" s="3">
         <v>40100</v>
       </c>
-      <c r="U42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3247,52 +3426,58 @@
       <c r="Z42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA42" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB42" s="3">
-        <v>0</v>
+      <c r="AA42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>200</v>
+      </c>
+      <c r="E43" s="3">
         <v>800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
+        <v>800</v>
+      </c>
+      <c r="G43" s="3">
         <v>1400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>200</v>
-      </c>
-      <c r="K43" s="3">
-        <v>200</v>
-      </c>
-      <c r="L43" s="3">
-        <v>100</v>
       </c>
       <c r="M43" s="3">
         <v>200</v>
       </c>
       <c r="N43" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O43" s="3">
         <v>200</v>
@@ -3310,19 +3495,19 @@
         <v>200</v>
       </c>
       <c r="T43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="U43" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="V43" s="3">
         <v>100</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X43" s="3" t="s">
-        <v>3</v>
+      <c r="W43" s="3">
+        <v>500</v>
+      </c>
+      <c r="X43" s="3">
+        <v>100</v>
       </c>
       <c r="Y43" s="3" t="s">
         <v>3</v>
@@ -3339,8 +3524,14 @@
       <c r="AC43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3377,11 +3568,11 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -3422,8 +3613,14 @@
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3460,36 +3657,36 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3">
         <v>800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>1500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>1400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>1800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>700</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3505,74 +3702,80 @@
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>18200</v>
+      </c>
+      <c r="E46" s="3">
+        <v>22200</v>
+      </c>
+      <c r="F46" s="3">
         <v>10500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>9300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>11200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>11600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>13700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>18500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>13900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>17800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>13200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>17300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>19300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>21100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>24300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>25800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>36400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>37700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>41600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>44300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>47400</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3588,8 +3791,14 @@
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3623,24 +3832,24 @@
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N47" s="3">
+      <c r="N47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3">
         <v>1000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>1900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>2900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>4900</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3653,11 +3862,11 @@
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X47" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y47" s="3">
-        <v>0</v>
+      <c r="X47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z47" s="3">
         <v>0</v>
@@ -3671,16 +3880,22 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E48" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="F48" s="3">
         <v>300</v>
@@ -3689,56 +3904,56 @@
         <v>300</v>
       </c>
       <c r="H48" s="3">
+        <v>300</v>
+      </c>
+      <c r="I48" s="3">
+        <v>300</v>
+      </c>
+      <c r="J48" s="3">
         <v>400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>1000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>1000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>1100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>1200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>1200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>600</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3754,8 +3969,14 @@
       <c r="AC48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3772,10 +3993,10 @@
         <v>100</v>
       </c>
       <c r="H49" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I49" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J49" s="3">
         <v>200</v>
@@ -3792,14 +4013,14 @@
       <c r="N49" s="3">
         <v>200</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
+      <c r="O49" s="3">
+        <v>200</v>
       </c>
       <c r="P49" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>0</v>
+        <v>200</v>
+      </c>
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R49" s="3">
         <v>0</v>
@@ -3837,8 +4058,14 @@
       <c r="AC49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3920,8 +4147,14 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4003,8 +4236,14 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4024,20 +4263,20 @@
         <v>100</v>
       </c>
       <c r="I52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3">
         <v>100</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
-      <c r="M52" s="3">
-        <v>0</v>
-      </c>
       <c r="N52" s="3">
         <v>0</v>
       </c>
@@ -4054,10 +4293,10 @@
         <v>0</v>
       </c>
       <c r="S52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U52" s="3">
         <v>100</v>
@@ -4065,11 +4304,11 @@
       <c r="V52" s="3">
         <v>100</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X52" s="3" t="s">
-        <v>3</v>
+      <c r="W52" s="3">
+        <v>100</v>
+      </c>
+      <c r="X52" s="3">
+        <v>100</v>
       </c>
       <c r="Y52" s="3" t="s">
         <v>3</v>
@@ -4086,8 +4325,14 @@
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4169,74 +4414,80 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>18700</v>
+      </c>
+      <c r="E54" s="3">
+        <v>22800</v>
+      </c>
+      <c r="F54" s="3">
         <v>11000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>9800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>11600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>12100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>14400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>19200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>14600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>18600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>14100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>18300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>21300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>24100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>28300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>31900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>37600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>39000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>42600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>45400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>48000</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4252,8 +4503,14 @@
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4283,8 +4540,10 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4314,74 +4573,76 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E57" s="3">
+        <v>800</v>
+      </c>
+      <c r="F57" s="3">
         <v>1600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>2700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>2200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>1100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>2000</v>
-      </c>
-      <c r="J57" s="3">
-        <v>1400</v>
-      </c>
-      <c r="K57" s="3">
-        <v>1300</v>
       </c>
       <c r="L57" s="3">
         <v>1400</v>
       </c>
       <c r="M57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="N57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="O57" s="3">
         <v>900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>2200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>1600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>1000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>2100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>1000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>900</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4397,8 +4658,14 @@
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4406,10 +4673,10 @@
         <v>200</v>
       </c>
       <c r="E58" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F58" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G58" s="3">
         <v>300</v>
@@ -4436,10 +4703,10 @@
         <v>300</v>
       </c>
       <c r="O58" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="P58" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="Q58" s="3">
         <v>100</v>
@@ -4457,13 +4724,13 @@
         <v>100</v>
       </c>
       <c r="V58" s="3">
-        <v>0</v>
-      </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X58" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="W58" s="3">
+        <v>100</v>
+      </c>
+      <c r="X58" s="3">
+        <v>0</v>
       </c>
       <c r="Y58" s="3" t="s">
         <v>3</v>
@@ -4480,74 +4747,80 @@
       <c r="AC58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E59" s="3">
+        <v>0</v>
+      </c>
+      <c r="F59" s="3">
         <v>100</v>
       </c>
-      <c r="E59" s="3">
-        <v>0</v>
-      </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
+        <v>0</v>
+      </c>
+      <c r="H59" s="3">
         <v>200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>1400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>100</v>
-      </c>
-      <c r="O59" s="3">
-        <v>2400</v>
-      </c>
-      <c r="P59" s="3">
-        <v>3200</v>
       </c>
       <c r="Q59" s="3">
         <v>2400</v>
       </c>
       <c r="R59" s="3">
+        <v>3200</v>
+      </c>
+      <c r="S59" s="3">
+        <v>2400</v>
+      </c>
+      <c r="T59" s="3">
         <v>2000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>1900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>2700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>1400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>1400</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4563,74 +4836,80 @@
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E60" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F60" s="3">
         <v>4200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>5200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>5000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>3900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>4600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>6500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>5000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>4900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>5800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>5600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>5200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>4100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>4300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>3400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>4200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>2600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>3600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>2500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>2300</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4646,58 +4925,64 @@
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>500</v>
+      </c>
+      <c r="E61" s="3">
+        <v>500</v>
+      </c>
+      <c r="F61" s="3">
         <v>400</v>
-      </c>
-      <c r="E61" s="3">
-        <v>400</v>
-      </c>
-      <c r="F61" s="3">
-        <v>300</v>
       </c>
       <c r="G61" s="3">
         <v>400</v>
       </c>
       <c r="H61" s="3">
+        <v>300</v>
+      </c>
+      <c r="I61" s="3">
+        <v>400</v>
+      </c>
+      <c r="J61" s="3">
         <v>500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>900</v>
-      </c>
-      <c r="O61" s="3">
-        <v>500</v>
-      </c>
-      <c r="P61" s="3">
-        <v>500</v>
       </c>
       <c r="Q61" s="3">
         <v>500</v>
       </c>
       <c r="R61" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="S61" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="T61" s="3">
         <v>600</v>
@@ -4706,14 +4991,14 @@
         <v>600</v>
       </c>
       <c r="V61" s="3">
+        <v>600</v>
+      </c>
+      <c r="W61" s="3">
+        <v>600</v>
+      </c>
+      <c r="X61" s="3">
         <v>700</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -4729,8 +5014,14 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4767,36 +5058,36 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O62" s="3">
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3">
         <v>600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>1000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>1000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>600</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4812,8 +5103,14 @@
       <c r="AC62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4895,8 +5192,14 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4978,8 +5281,14 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5061,74 +5370,80 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>4300</v>
+      </c>
+      <c r="F66" s="3">
         <v>5100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>6100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>5800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>4800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>5500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>7400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>5900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>6000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>6800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>7200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>6200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>5200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>5700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>4900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>5800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>4200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>5000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>4000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>3600</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5144,8 +5459,14 @@
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5175,8 +5496,10 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5258,8 +5581,14 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5341,8 +5670,14 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5424,8 +5759,14 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5507,74 +5848,80 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-107000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-101400</v>
+      </c>
+      <c r="F72" s="3">
         <v>-96800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-91500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-85700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-81200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-77400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-72900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-64800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-60800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-56100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-51300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-43700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-38500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-33800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-29300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-24200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-20900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-17700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-13000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-9500</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5590,8 +5937,14 @@
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5673,8 +6026,14 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5756,8 +6115,14 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5839,74 +6204,80 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>18600</v>
+      </c>
+      <c r="F76" s="3">
         <v>5900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>3700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>5800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>7300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>8900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>11800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>8600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>12600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>7300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>11100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>15100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>18900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>22700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>27000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>31800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>34800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>37500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>41400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>44500</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5922,8 +6293,14 @@
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6005,85 +6382,91 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
@@ -6093,80 +6476,86 @@
       <c r="AC80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="F81" s="3">
         <v>-5300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-5800</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-3800</v>
       </c>
       <c r="H81" s="3">
         <v>-4500</v>
       </c>
       <c r="I81" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="J81" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="K81" s="3">
         <v>-8100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-4000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-4700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-4700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-7700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-5100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-4700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-5100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-3300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-3200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-4700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-3600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-2500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-600</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
@@ -6176,8 +6565,14 @@
       <c r="AC81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6207,8 +6602,10 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6275,11 +6672,11 @@
       <c r="X83" s="3">
         <v>0</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z83" s="3" t="s">
-        <v>3</v>
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z83" s="3">
+        <v>0</v>
       </c>
       <c r="AA83" s="3" t="s">
         <v>3</v>
@@ -6290,8 +6687,14 @@
       <c r="AC83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6373,8 +6776,14 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6456,8 +6865,14 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6539,8 +6954,14 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6622,8 +7043,14 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6705,80 +7132,86 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="F89" s="3">
         <v>-4900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-5100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-3800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-3500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-6100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-5800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-3600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-5700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-4000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-5000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-4200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-3900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-5100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-2400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-4100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-2200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-3200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-2800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-800</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6788,8 +7221,14 @@
       <c r="AC89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6819,8 +7258,10 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6833,23 +7274,23 @@
       <c r="F91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I91" s="3">
         <v>0</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>3</v>
+      <c r="J91" s="3">
+        <v>0</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -6858,14 +7299,14 @@
         <v>0</v>
       </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
@@ -6887,11 +7328,11 @@
       <c r="X91" s="3">
         <v>0</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z91" s="3" t="s">
-        <v>3</v>
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
+        <v>0</v>
       </c>
       <c r="AA91" s="3" t="s">
         <v>3</v>
@@ -6902,8 +7343,14 @@
       <c r="AC91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6985,8 +7432,14 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7068,8 +7521,14 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7082,45 +7541,45 @@
       <c r="F94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
+      <c r="G94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>2000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>3000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>3100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>1900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>3000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>2100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>100</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
         <v>-14900</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
       <c r="T94" s="3">
         <v>0</v>
       </c>
@@ -7136,11 +7595,11 @@
       <c r="X94" s="3">
         <v>0</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z94" s="3" t="s">
-        <v>3</v>
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
+        <v>0</v>
       </c>
       <c r="AA94" s="3" t="s">
         <v>3</v>
@@ -7151,8 +7610,14 @@
       <c r="AC94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7182,8 +7647,10 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7220,11 +7687,11 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -7265,8 +7732,14 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7348,8 +7821,14 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7431,8 +7910,14 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7514,50 +7999,56 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>400</v>
+      </c>
+      <c r="E100" s="3">
+        <v>16600</v>
+      </c>
+      <c r="F100" s="3">
         <v>7000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>2500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>2400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>2300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>10000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>9600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>2200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>700</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
         <v>0</v>
       </c>
@@ -7571,23 +8062,23 @@
         <v>0</v>
       </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>-200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>42000</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>1400</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7597,65 +8088,71 @@
       <c r="AC100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>100</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F101" s="3">
         <v>400</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>-400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>100</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
         <v>200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-100</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
         <v>200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-100</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
         <v>100</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
       <c r="V101" s="3">
         <v>0</v>
       </c>
@@ -7665,11 +8162,11 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-      <c r="Y101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z101" s="3" t="s">
-        <v>3</v>
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
+        <v>0</v>
       </c>
       <c r="AA101" s="3" t="s">
         <v>3</v>
@@ -7680,80 +8177,86 @@
       <c r="AC101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E102" s="3">
+        <v>12000</v>
+      </c>
+      <c r="F102" s="3">
         <v>2100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-2400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-1300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-1700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-4900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>6300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-1200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>7500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-2000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-1300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-3600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-20000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-2500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-4100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-2200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-3400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>39100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>600</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7761,6 +8264,12 @@
         <v>3</v>
       </c>
       <c r="AC102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
